--- a/results/01_pollution_assessment/MaxRel_Focus/tables/env_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/env_cutoff_metrics.xlsx
@@ -491,28 +491,28 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.454064776694675</v>
+        <v>0.497229525129012</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.09187044661064991</v>
+        <v>-0.005540949741976053</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8317191441606807</v>
+        <v>0.9889791664011348</v>
       </c>
       <c r="G2" t="n">
-        <v>0.663</v>
+        <v>0.517</v>
       </c>
       <c r="H2" t="n">
-        <v>155.8593159772075</v>
+        <v>2.565558931893026</v>
       </c>
       <c r="I2" t="n">
-        <v>343.25348271181</v>
+        <v>5.159707543970486</v>
       </c>
       <c r="J2" t="n">
-        <v>9.15232281063167</v>
+        <v>0.2024257857693038</v>
       </c>
       <c r="K2" t="n">
-        <v>12.04855889644246</v>
+        <v>9.499101272840637</v>
       </c>
     </row>
     <row r="3">
@@ -526,28 +526,28 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3375533790435992</v>
+        <v>0.362683019842467</v>
       </c>
       <c r="E3" t="n">
-        <v>0.00633006856539875</v>
+        <v>0.04402452976370064</v>
       </c>
       <c r="F3" t="n">
-        <v>1.019111180780905</v>
+        <v>1.138155834959296</v>
       </c>
       <c r="G3" t="n">
-        <v>0.448</v>
+        <v>0.338</v>
       </c>
       <c r="H3" t="n">
-        <v>149.7692047607856</v>
+        <v>2.867092576922619</v>
       </c>
       <c r="I3" t="n">
-        <v>443.6904325624929</v>
+        <v>7.905229691116926</v>
       </c>
       <c r="J3" t="n">
-        <v>6.190782085358384</v>
+        <v>0.1465055446309235</v>
       </c>
       <c r="K3" t="n">
-        <v>4.107002905383196</v>
+        <v>5.805982957435718</v>
       </c>
     </row>
     <row r="4">
@@ -561,28 +561,28 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2690628190827336</v>
+        <v>0.2558352404892725</v>
       </c>
       <c r="E4" t="n">
-        <v>0.008013825897995486</v>
+        <v>-0.009937887907415899</v>
       </c>
       <c r="F4" t="n">
-        <v>1.030698551257481</v>
+        <v>0.962607627161679</v>
       </c>
       <c r="G4" t="n">
-        <v>0.45</v>
+        <v>0.506</v>
       </c>
       <c r="H4" t="n">
-        <v>148.9924651300704</v>
+        <v>2.6368237255011</v>
       </c>
       <c r="I4" t="n">
-        <v>553.7460197510866</v>
+        <v>10.3067260024784</v>
       </c>
       <c r="J4" t="n">
-        <v>4.669555028397693</v>
+        <v>0.09020054841811048</v>
       </c>
       <c r="K4" t="n">
-        <v>3.791297481833243</v>
+        <v>3.76250275686638</v>
       </c>
     </row>
     <row r="5">
@@ -596,28 +596,28 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2490882289063757</v>
+        <v>0.2356343537906873</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05147986809226412</v>
+        <v>0.03448549952507873</v>
       </c>
       <c r="F5" t="n">
-        <v>1.26051462539427</v>
+        <v>1.171442684329397</v>
       </c>
       <c r="G5" t="n">
-        <v>0.173</v>
+        <v>0.278</v>
       </c>
       <c r="H5" t="n">
-        <v>177.0048403230226</v>
+        <v>2.941528490386848</v>
       </c>
       <c r="I5" t="n">
-        <v>710.6110196381584</v>
+        <v>12.48344497763595</v>
       </c>
       <c r="J5" t="n">
-        <v>3.981816140151955</v>
+        <v>0.07449769443232448</v>
       </c>
       <c r="K5" t="n">
-        <v>1.715695828718381</v>
+        <v>3.453666067834401</v>
       </c>
     </row>
     <row r="6">
@@ -631,28 +631,28 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2290282931613529</v>
+        <v>0.202966683733261</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06840918756996828</v>
+        <v>0.03691807617769038</v>
       </c>
       <c r="F6" t="n">
-        <v>1.425909404227422</v>
+        <v>1.222332946485776</v>
       </c>
       <c r="G6" t="n">
-        <v>0.082</v>
+        <v>0.242</v>
       </c>
       <c r="H6" t="n">
-        <v>187.984513179906</v>
+        <v>2.935322066650834</v>
       </c>
       <c r="I6" t="n">
-        <v>820.7916610873438</v>
+        <v>14.46208812530256</v>
       </c>
       <c r="J6" t="n">
-        <v>3.660958835599077</v>
+        <v>0.06762898153473279</v>
       </c>
       <c r="K6" t="n">
-        <v>1.964696733205971</v>
+        <v>2.138005127264277</v>
       </c>
     </row>
     <row r="7">
@@ -666,28 +666,28 @@
         <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2256937344639147</v>
+        <v>0.2155392725494269</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08742475847532805</v>
+        <v>0.07545699979039588</v>
       </c>
       <c r="F7" t="n">
-        <v>1.63228036405321</v>
+        <v>1.538662018428248</v>
       </c>
       <c r="G7" t="n">
-        <v>0.027</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>199.835450994064</v>
+        <v>3.537904715154093</v>
       </c>
       <c r="I7" t="n">
-        <v>885.4275528238688</v>
+        <v>16.41419994280991</v>
       </c>
       <c r="J7" t="n">
-        <v>3.44774026972483</v>
+        <v>0.07852123067006236</v>
       </c>
       <c r="K7" t="n">
-        <v>1.964464721270897</v>
+        <v>2.07152114076263</v>
       </c>
     </row>
     <row r="8">
@@ -701,28 +701,28 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2041629597528988</v>
+        <v>0.2406614020034559</v>
       </c>
       <c r="E8" t="n">
-        <v>0.08358159001848942</v>
+        <v>0.1256100992767067</v>
       </c>
       <c r="F8" t="n">
-        <v>1.693155088572847</v>
+        <v>2.091774680509572</v>
       </c>
       <c r="G8" t="n">
-        <v>0.026</v>
+        <v>0.007</v>
       </c>
       <c r="H8" t="n">
-        <v>194.4687604532767</v>
+        <v>4.546080817089507</v>
       </c>
       <c r="I8" t="n">
-        <v>952.5173454021478</v>
+        <v>18.88994570481321</v>
       </c>
       <c r="J8" t="n">
-        <v>3.037457404256477</v>
+        <v>0.08201465976108782</v>
       </c>
       <c r="K8" t="n">
-        <v>1.728689704260555</v>
+        <v>1.747340313866239</v>
       </c>
     </row>
     <row r="9">
@@ -736,28 +736,28 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2171090769975939</v>
+        <v>0.227504156184188</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1140971134446458</v>
+        <v>0.1258599662084232</v>
       </c>
       <c r="F9" t="n">
-        <v>2.107610315436807</v>
+        <v>2.238240633708944</v>
       </c>
       <c r="G9" t="n">
-        <v>0.005</v>
+        <v>0.007</v>
       </c>
       <c r="H9" t="n">
-        <v>237.7647795625754</v>
+        <v>4.705756602424207</v>
       </c>
       <c r="I9" t="n">
-        <v>1095.139746576373</v>
+        <v>20.6842665266054</v>
       </c>
       <c r="J9" t="n">
-        <v>3.53585325699427</v>
+        <v>0.07561571516162249</v>
       </c>
       <c r="K9" t="n">
-        <v>1.457393357759886</v>
+        <v>1.638443591008128</v>
       </c>
     </row>
     <row r="10">
@@ -771,28 +771,28 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2164837485069396</v>
+        <v>0.2461834002386351</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1232080042815753</v>
+        <v>0.1564433288384726</v>
       </c>
       <c r="F10" t="n">
-        <v>2.320900790498024</v>
+        <v>2.743294008992612</v>
       </c>
       <c r="G10" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>265.8135459136413</v>
+        <v>5.612214642086499</v>
       </c>
       <c r="I10" t="n">
-        <v>1227.868363084633</v>
+        <v>22.7968849103813</v>
       </c>
       <c r="J10" t="n">
-        <v>3.467782559166392</v>
+        <v>0.08931103097109075</v>
       </c>
       <c r="K10" t="n">
-        <v>1.360664138485756</v>
+        <v>1.508631271790515</v>
       </c>
     </row>
     <row r="11">
@@ -806,28 +806,28 @@
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2491154112060492</v>
+        <v>0.2020004161205684</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1692340719726502</v>
+        <v>0.1171068433674374</v>
       </c>
       <c r="F11" t="n">
-        <v>3.118568286370092</v>
+        <v>2.379454764001769</v>
       </c>
       <c r="G11" t="n">
-        <v>0.001</v>
+        <v>0.003</v>
       </c>
       <c r="H11" t="n">
-        <v>355.8637443138059</v>
+        <v>4.976230906224685</v>
       </c>
       <c r="I11" t="n">
-        <v>1428.509551420176</v>
+        <v>24.63475571879274</v>
       </c>
       <c r="J11" t="n">
-        <v>4.89892879435626</v>
+        <v>0.06763969625822487</v>
       </c>
       <c r="K11" t="n">
-        <v>1.320637831680014</v>
+        <v>1.198096996920468</v>
       </c>
     </row>
     <row r="12">
@@ -841,28 +841,28 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2611641873873116</v>
+        <v>0.2072009476532409</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1901222823283992</v>
+        <v>0.1309702695429755</v>
       </c>
       <c r="F12" t="n">
-        <v>3.676199099260334</v>
+        <v>2.718078243427549</v>
       </c>
       <c r="G12" t="n">
         <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>414.575140295981</v>
+        <v>5.755195414681758</v>
       </c>
       <c r="I12" t="n">
-        <v>1587.411905297559</v>
+        <v>27.77591260978839</v>
       </c>
       <c r="J12" t="n">
-        <v>5.421913695254542</v>
+        <v>0.06926089161108721</v>
       </c>
       <c r="K12" t="n">
-        <v>1.382322438976155</v>
+        <v>1.192142318651783</v>
       </c>
     </row>
     <row r="13">
@@ -876,28 +876,28 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2596740034226864</v>
+        <v>0.1956147144569446</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1935734680139978</v>
+        <v>0.1237945996763147</v>
       </c>
       <c r="F13" t="n">
-        <v>3.928470500536264</v>
+        <v>2.723675881811628</v>
       </c>
       <c r="G13" t="n">
         <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>450.9244023184477</v>
+        <v>5.678981192679139</v>
       </c>
       <c r="I13" t="n">
-        <v>1736.501907680192</v>
+        <v>29.03146222125893</v>
       </c>
       <c r="J13" t="n">
-        <v>5.542146240870018</v>
+        <v>0.06462539201775121</v>
       </c>
       <c r="K13" t="n">
-        <v>1.407756773393111</v>
+        <v>1.202788401670979</v>
       </c>
     </row>
     <row r="14">
@@ -911,28 +911,28 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2286852390593463</v>
+        <v>0.1958287236647548</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1654627176707681</v>
+        <v>0.12991304527662</v>
       </c>
       <c r="F14" t="n">
-        <v>3.617148352148145</v>
+        <v>2.970897492879402</v>
       </c>
       <c r="G14" t="n">
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>423.7689487047987</v>
+        <v>5.885261041146888</v>
       </c>
       <c r="I14" t="n">
-        <v>1853.066470087412</v>
+        <v>30.05310421785747</v>
       </c>
       <c r="J14" t="n">
-        <v>4.831600427020527</v>
+        <v>0.06283596132881994</v>
       </c>
       <c r="K14" t="n">
-        <v>1.217222563494262</v>
+        <v>1.192628746553563</v>
       </c>
     </row>
     <row r="15">
@@ -946,28 +946,28 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2007699431303815</v>
+        <v>0.1584090861729938</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1402222115493499</v>
+        <v>0.09465219876185693</v>
       </c>
       <c r="F15" t="n">
-        <v>3.315895375232824</v>
+        <v>2.484579981947541</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>400.7771584283194</v>
+        <v>4.961027298884605</v>
       </c>
       <c r="I15" t="n">
-        <v>1996.200985961587</v>
+        <v>31.31782032671293</v>
       </c>
       <c r="J15" t="n">
-        <v>4.30066557440308</v>
+        <v>0.04839043811674677</v>
       </c>
       <c r="K15" t="n">
-        <v>1.251240134904972</v>
+        <v>1.205088974378534</v>
       </c>
     </row>
     <row r="16">
@@ -981,28 +981,28 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.200816896175194</v>
+        <v>0.1712383201715743</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1437323887591365</v>
+        <v>0.1120410573266869</v>
       </c>
       <c r="F16" t="n">
-        <v>3.517887869497589</v>
+        <v>2.892672936927233</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>429.6952753753978</v>
+        <v>5.731630851746091</v>
       </c>
       <c r="I16" t="n">
-        <v>2139.736663395737</v>
+        <v>33.47166011674965</v>
       </c>
       <c r="J16" t="n">
-        <v>4.405752670014365</v>
+        <v>0.05504833728506429</v>
       </c>
       <c r="K16" t="n">
-        <v>1.237245253108724</v>
+        <v>1.235848094617273</v>
       </c>
     </row>
     <row r="17">
@@ -1016,28 +1016,28 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1794150350020618</v>
+        <v>0.1615294040545064</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1247093706688659</v>
+        <v>0.1056313643248068</v>
       </c>
       <c r="F17" t="n">
-        <v>3.279642742464444</v>
+        <v>2.889715003166437</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>407.376969476421</v>
+        <v>5.666659808775734</v>
       </c>
       <c r="I17" t="n">
-        <v>2270.584343568194</v>
+        <v>35.08128963853281</v>
       </c>
       <c r="J17" t="n">
-        <v>3.907193209204037</v>
+        <v>0.05117394519578227</v>
       </c>
       <c r="K17" t="n">
-        <v>1.210891217940737</v>
+        <v>1.238102230181861</v>
       </c>
     </row>
     <row r="18">
@@ -1051,28 +1051,28 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1779500355663928</v>
+        <v>0.1449374684574826</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1265719127892924</v>
+        <v>0.09149606023607526</v>
       </c>
       <c r="F18" t="n">
-        <v>3.463537123347493</v>
+        <v>2.712081759840755</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>423.0218300961283</v>
+        <v>5.498014450622271</v>
       </c>
       <c r="I18" t="n">
-        <v>2377.19441162067</v>
+        <v>37.93370002343538</v>
       </c>
       <c r="J18" t="n">
-        <v>3.875880155216715</v>
+        <v>0.04833282094224045</v>
       </c>
       <c r="K18" t="n">
-        <v>1.217545387503831</v>
+        <v>1.256619408695372</v>
       </c>
     </row>
     <row r="19">
@@ -1086,28 +1086,28 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1801093091118439</v>
+        <v>0.1422528615963377</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1313062917970728</v>
+        <v>0.09119648431040539</v>
       </c>
       <c r="F19" t="n">
-        <v>3.690536344303659</v>
+        <v>2.786191836519765</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>444.3413602864089</v>
+        <v>5.526071485582287</v>
       </c>
       <c r="I19" t="n">
-        <v>2467.064931166232</v>
+        <v>38.84682124190434</v>
       </c>
       <c r="J19" t="n">
-        <v>3.990592698089626</v>
+        <v>0.04737344038262722</v>
       </c>
       <c r="K19" t="n">
-        <v>1.234444089636111</v>
+        <v>1.215104032616906</v>
       </c>
     </row>
     <row r="20">
@@ -1121,28 +1121,28 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1812893623035288</v>
+        <v>0.1752041438020825</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1352943826576597</v>
+        <v>0.128867297948267</v>
       </c>
       <c r="F20" t="n">
-        <v>3.941503261863284</v>
+        <v>3.781097754362048</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>471.4850423811632</v>
+        <v>7.527032471112671</v>
       </c>
       <c r="I20" t="n">
-        <v>2600.731981128414</v>
+        <v>42.96149798611786</v>
       </c>
       <c r="J20" t="n">
-        <v>4.092750561468099</v>
+        <v>0.06704050156586738</v>
       </c>
       <c r="K20" t="n">
-        <v>1.251405768935727</v>
+        <v>1.247082934141258</v>
       </c>
     </row>
     <row r="21">
@@ -1156,28 +1156,28 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1748967880624037</v>
+        <v>0.1749839917670264</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1310083193423189</v>
+        <v>0.1311001615418683</v>
       </c>
       <c r="F21" t="n">
-        <v>3.985028258285182</v>
+        <v>3.987436622309915</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>482.4602509001282</v>
+        <v>7.878211222635999</v>
       </c>
       <c r="I21" t="n">
-        <v>2758.542659616967</v>
+        <v>45.02246830170068</v>
       </c>
       <c r="J21" t="n">
-        <v>3.915466250254442</v>
+        <v>0.06492950275632782</v>
       </c>
       <c r="K21" t="n">
-        <v>1.260780127594664</v>
+        <v>1.24199407636883</v>
       </c>
     </row>
     <row r="22">
@@ -1191,28 +1191,28 @@
         <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1693897411386435</v>
+        <v>0.1600180586269882</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1270116667069416</v>
+        <v>0.1171618371283651</v>
       </c>
       <c r="F22" t="n">
-        <v>3.99710801895066</v>
+        <v>3.733834972645207</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>480.3095104593779</v>
+        <v>7.487263008734812</v>
       </c>
       <c r="I22" t="n">
-        <v>2835.528924188215</v>
+        <v>46.79011277213453</v>
       </c>
       <c r="J22" t="n">
-        <v>3.73463631054317</v>
+        <v>0.05992674953692851</v>
       </c>
       <c r="K22" t="n">
-        <v>1.250764861472867</v>
+        <v>1.234102768844652</v>
       </c>
     </row>
     <row r="23">
@@ -1226,28 +1226,28 @@
         <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1719684363777779</v>
+        <v>0.1544569110394849</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1317727294058254</v>
+        <v>0.1134111300219842</v>
       </c>
       <c r="F23" t="n">
-        <v>4.278278685277826</v>
+        <v>3.763039884017044</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>512.6168055202993</v>
+        <v>7.556120648359236</v>
       </c>
       <c r="I23" t="n">
-        <v>2980.877283748686</v>
+        <v>48.92057336578231</v>
       </c>
       <c r="J23" t="n">
-        <v>3.86415697019804</v>
+        <v>0.05796578752922536</v>
       </c>
       <c r="K23" t="n">
-        <v>1.258971861511684</v>
+        <v>1.206044823933059</v>
       </c>
     </row>
     <row r="24">
@@ -1261,28 +1261,28 @@
         <v>114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1656348374493649</v>
+        <v>0.1523015830061783</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1270068206646133</v>
+        <v>0.1130562859231311</v>
       </c>
       <c r="F24" t="n">
-        <v>4.287945673533753</v>
+        <v>3.880760099328377</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>514.5086984406422</v>
+        <v>7.874687210458195</v>
       </c>
       <c r="I24" t="n">
-        <v>3106.283112681106</v>
+        <v>51.70456573743391</v>
       </c>
       <c r="J24" t="n">
-        <v>3.729092756402996</v>
+        <v>0.05766099161477416</v>
       </c>
       <c r="K24" t="n">
-        <v>1.259026209277605</v>
+        <v>1.216477571429641</v>
       </c>
     </row>
     <row r="25">
@@ -1296,28 +1296,28 @@
         <v>118</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1659716421051018</v>
+        <v>0.1587769292215391</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1287382332705082</v>
+        <v>0.1212223278475006</v>
       </c>
       <c r="F25" t="n">
-        <v>4.457599970027377</v>
+        <v>4.22789547518142</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>535.5348976590851</v>
+        <v>8.632978520192564</v>
       </c>
       <c r="I25" t="n">
-        <v>3226.665054744453</v>
+        <v>54.37174382020638</v>
       </c>
       <c r="J25" t="n">
-        <v>3.68175347146555</v>
+        <v>0.06215791494785122</v>
       </c>
       <c r="K25" t="n">
-        <v>1.257588786064872</v>
+        <v>1.225943713504539</v>
       </c>
     </row>
     <row r="26">
@@ -1331,28 +1331,28 @@
         <v>123</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1708156489504474</v>
+        <v>0.1561463138065758</v>
       </c>
       <c r="E26" t="n">
-        <v>0.135380420273116</v>
+        <v>0.1200841904649764</v>
       </c>
       <c r="F26" t="n">
-        <v>4.82050364358794</v>
+        <v>4.329925676518717</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>574.897430022305</v>
+        <v>8.752251075143983</v>
       </c>
       <c r="I26" t="n">
-        <v>3365.601650403116</v>
+        <v>56.05160225546993</v>
       </c>
       <c r="J26" t="n">
-        <v>3.825871802688665</v>
+        <v>0.06044080359204083</v>
       </c>
       <c r="K26" t="n">
-        <v>1.261578931185537</v>
+        <v>1.227326111231638</v>
       </c>
     </row>
     <row r="27">
@@ -1366,28 +1366,28 @@
         <v>128</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1679189404399182</v>
+        <v>0.1629936691051306</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1338172576710625</v>
+        <v>0.1286901309537015</v>
       </c>
       <c r="F27" t="n">
-        <v>4.924066110698629</v>
+        <v>4.751511881532847</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>582.7173807094449</v>
+        <v>9.702957258828125</v>
       </c>
       <c r="I27" t="n">
-        <v>3470.23021454773</v>
+        <v>59.52965726889514</v>
       </c>
       <c r="J27" t="n">
-        <v>3.70162644333443</v>
+        <v>0.06513888145763021</v>
       </c>
       <c r="K27" t="n">
-        <v>1.248300844932213</v>
+        <v>1.256179197144718</v>
       </c>
     </row>
     <row r="28">
@@ -1401,28 +1401,28 @@
         <v>132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1898143693767542</v>
+        <v>0.1633653691685864</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1576641459393238</v>
+        <v>0.1301655822308319</v>
       </c>
       <c r="F28" t="n">
-        <v>5.903982899097548</v>
+        <v>4.920675228274095</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>694.3279792393403</v>
+        <v>9.97588831769793</v>
       </c>
       <c r="I28" t="n">
-        <v>3657.931596639026</v>
+        <v>61.06489012003038</v>
       </c>
       <c r="J28" t="n">
-        <v>4.40279067600661</v>
+        <v>0.06534494031331908</v>
       </c>
       <c r="K28" t="n">
-        <v>1.274542956522154</v>
+        <v>1.232262433822034</v>
       </c>
     </row>
     <row r="29">
@@ -1436,28 +1436,28 @@
         <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1866738930901128</v>
+        <v>0.1764342253371078</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1556309119103462</v>
+        <v>0.1450004171438677</v>
       </c>
       <c r="F29" t="n">
-        <v>6.013400968454148</v>
+        <v>5.61288101818506</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>703.1646919310972</v>
+        <v>11.23362432134531</v>
       </c>
       <c r="I29" t="n">
-        <v>3766.807882405171</v>
+        <v>63.67032416687606</v>
       </c>
       <c r="J29" t="n">
-        <v>4.252153723259522</v>
+        <v>0.0710576490797504</v>
       </c>
       <c r="K29" t="n">
-        <v>1.261178387169282</v>
+        <v>1.279991572266424</v>
       </c>
     </row>
     <row r="30">
@@ -1471,28 +1471,28 @@
         <v>142</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1865757374183129</v>
+        <v>0.1921549516849918</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1566704336469272</v>
+        <v>0.1624547660851753</v>
       </c>
       <c r="F30" t="n">
-        <v>6.238884541839536</v>
+        <v>6.469823262187936</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>724.8835435249124</v>
+        <v>12.77490667020447</v>
       </c>
       <c r="I30" t="n">
-        <v>3885.197258525015</v>
+        <v>66.48231834871964</v>
       </c>
       <c r="J30" t="n">
-        <v>4.24045410663471</v>
+        <v>0.07970906715472528</v>
       </c>
       <c r="K30" t="n">
-        <v>1.246816721843027</v>
+        <v>1.295766298011334</v>
       </c>
     </row>
     <row r="31">
@@ -1506,28 +1506,28 @@
         <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1843405653621115</v>
+        <v>0.188083657457276</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1552098712679011</v>
+        <v>0.1590866452236073</v>
       </c>
       <c r="F31" t="n">
-        <v>6.32805262950288</v>
+        <v>6.486311622094993</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>735.4403061166389</v>
+        <v>12.94796616613969</v>
       </c>
       <c r="I31" t="n">
-        <v>3989.573888264735</v>
+        <v>68.84152690980542</v>
       </c>
       <c r="J31" t="n">
-        <v>4.120503580109236</v>
+        <v>0.07844337514611927</v>
       </c>
       <c r="K31" t="n">
-        <v>1.252416261839616</v>
+        <v>1.272049585058742</v>
       </c>
     </row>
     <row r="32">
@@ -1541,28 +1541,28 @@
         <v>151</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1964941516440949</v>
+        <v>0.18792162834294</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1687870534249257</v>
+        <v>0.1599189258720067</v>
       </c>
       <c r="F32" t="n">
-        <v>7.091834377233718</v>
+        <v>6.710839017698497</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>826.975102950909</v>
+        <v>13.35601619833081</v>
       </c>
       <c r="I32" t="n">
-        <v>4208.649957423613</v>
+        <v>71.07226728557976</v>
       </c>
       <c r="J32" t="n">
-        <v>4.613896777623492</v>
+        <v>0.07832950725569948</v>
       </c>
       <c r="K32" t="n">
-        <v>1.332565717479561</v>
+        <v>1.27129152495296</v>
       </c>
     </row>
     <row r="33">
@@ -1576,28 +1576,28 @@
         <v>156</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1909420999615216</v>
+        <v>0.1872152835215359</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1639735032935722</v>
+        <v>0.1601224596389202</v>
       </c>
       <c r="F33" t="n">
-        <v>7.08016447101402</v>
+        <v>6.910142860437131</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>829.6509627524453</v>
+        <v>13.87964955332536</v>
       </c>
       <c r="I33" t="n">
-        <v>4345.039480133692</v>
+        <v>74.13737432248017</v>
       </c>
       <c r="J33" t="n">
-        <v>4.416299335543785</v>
+        <v>0.07981280278600013</v>
       </c>
       <c r="K33" t="n">
-        <v>1.290605022228659</v>
+        <v>1.286237448189681</v>
       </c>
     </row>
     <row r="34">
@@ -1611,28 +1611,28 @@
         <v>160</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1876318024444358</v>
+        <v>0.1844163686913182</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1612562116147096</v>
+        <v>0.1579363806618156</v>
       </c>
       <c r="F34" t="n">
-        <v>7.113842630322004</v>
+        <v>6.964367524858807</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>830.7790011658849</v>
+        <v>13.96348312012855</v>
       </c>
       <c r="I34" t="n">
-        <v>4427.708897652928</v>
+        <v>75.71715688373116</v>
       </c>
       <c r="J34" t="n">
-        <v>4.367324964565436</v>
+        <v>0.07812895568695974</v>
       </c>
       <c r="K34" t="n">
-        <v>1.293362536419156</v>
+        <v>1.289054894447494</v>
       </c>
     </row>
     <row r="35">
@@ -1646,28 +1646,28 @@
         <v>165</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1912594112921338</v>
+        <v>0.1863159022706069</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1658273173076097</v>
+        <v>0.1607283520275442</v>
       </c>
       <c r="F35" t="n">
-        <v>7.520395741244064</v>
+        <v>7.28150606450186</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>871.9509590643797</v>
+        <v>14.58647520795661</v>
       </c>
       <c r="I35" t="n">
-        <v>4558.996355648836</v>
+        <v>78.28894383245442</v>
       </c>
       <c r="J35" t="n">
-        <v>4.470009394257561</v>
+        <v>0.07861916684670875</v>
       </c>
       <c r="K35" t="n">
-        <v>1.305935409133459</v>
+        <v>1.29801977536493</v>
       </c>
     </row>
     <row r="36">
@@ -1681,28 +1681,28 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1977795627045709</v>
+        <v>0.1770374342736645</v>
       </c>
       <c r="E36" t="n">
-        <v>0.173321622543125</v>
+        <v>0.1519471121478615</v>
       </c>
       <c r="F36" t="n">
-        <v>8.086517564399742</v>
+        <v>7.056004836685577</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>928.9421551934211</v>
+        <v>14.30171721474321</v>
       </c>
       <c r="I36" t="n">
-        <v>4696.856148787268</v>
+        <v>80.78357706334363</v>
       </c>
       <c r="J36" t="n">
-        <v>4.65087267708745</v>
+        <v>0.07501146775061275</v>
       </c>
       <c r="K36" t="n">
-        <v>1.294435438861182</v>
+        <v>1.291723506782565</v>
       </c>
     </row>
     <row r="37">
@@ -1716,28 +1716,28 @@
         <v>174</v>
       </c>
       <c r="D37" t="n">
-        <v>0.2011093034817221</v>
+        <v>0.1845319601544374</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1773327946567734</v>
+        <v>0.1602620780161766</v>
       </c>
       <c r="F37" t="n">
-        <v>8.458319300043648</v>
+        <v>7.603331532604684</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>963.7787172298431</v>
+        <v>15.3551387832189</v>
       </c>
       <c r="I37" t="n">
-        <v>4792.312939005513</v>
+        <v>83.21127012560841</v>
       </c>
       <c r="J37" t="n">
-        <v>4.74511231262591</v>
+        <v>0.07972411141048599</v>
       </c>
       <c r="K37" t="n">
-        <v>1.306730479193242</v>
+        <v>1.289824679652318</v>
       </c>
     </row>
     <row r="38">
@@ -1751,28 +1751,28 @@
         <v>179</v>
       </c>
       <c r="D38" t="n">
-        <v>0.196790802350151</v>
+        <v>0.1976598587505477</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1735766636897507</v>
+        <v>0.1744708373271531</v>
       </c>
       <c r="F38" t="n">
-        <v>8.477195954974015</v>
+        <v>8.523855109777754</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>967.3026022796028</v>
+        <v>17.04592170097868</v>
       </c>
       <c r="I38" t="n">
-        <v>4915.385224958205</v>
+        <v>86.23866175322485</v>
       </c>
       <c r="J38" t="n">
-        <v>4.622249544946824</v>
+        <v>0.08678708197962093</v>
       </c>
       <c r="K38" t="n">
-        <v>1.306441872503319</v>
+        <v>1.266444647511108</v>
       </c>
     </row>
     <row r="39">
@@ -1786,28 +1786,28 @@
         <v>184</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1998056512523499</v>
+        <v>0.1943875202304184</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1773282819055058</v>
+        <v>0.171757956191947</v>
       </c>
       <c r="F39" t="n">
-        <v>8.889191976569235</v>
+        <v>8.589980783542709</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>1003.08029839762</v>
+        <v>17.16264204753859</v>
       </c>
       <c r="I39" t="n">
-        <v>5020.279917562256</v>
+        <v>88.29086366858712</v>
       </c>
       <c r="J39" t="n">
-        <v>4.709001941985296</v>
+        <v>0.08560830941369901</v>
       </c>
       <c r="K39" t="n">
-        <v>1.29802422212524</v>
+        <v>1.249385797859496</v>
       </c>
     </row>
     <row r="40">
@@ -1821,28 +1821,28 @@
         <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2003347081567008</v>
+        <v>0.2072824330432303</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1783658814577092</v>
+        <v>0.1855044779070555</v>
       </c>
       <c r="F40" t="n">
-        <v>9.119044494346861</v>
+        <v>9.517993390431638</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>1016.214231057628</v>
+        <v>18.89673452555497</v>
       </c>
       <c r="I40" t="n">
-        <v>5072.581982462818</v>
+        <v>91.16418718229689</v>
       </c>
       <c r="J40" t="n">
-        <v>4.674361523025191</v>
+        <v>0.09186230640978409</v>
       </c>
       <c r="K40" t="n">
-        <v>1.281989702700115</v>
+        <v>1.261837441994162</v>
       </c>
     </row>
     <row r="41">
@@ -1856,28 +1856,28 @@
         <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2004832439013848</v>
+        <v>0.206225208488714</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1791057905297639</v>
+        <v>0.1850012835819951</v>
       </c>
       <c r="F41" t="n">
-        <v>9.378256634044767</v>
+        <v>9.716638623397559</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>1035.149830666143</v>
+        <v>19.12463638290981</v>
       </c>
       <c r="I41" t="n">
-        <v>5163.273551057066</v>
+        <v>92.73665679895012</v>
       </c>
       <c r="J41" t="n">
-        <v>4.631984768158485</v>
+        <v>0.08990168774592108</v>
       </c>
       <c r="K41" t="n">
-        <v>1.271124101369079</v>
+        <v>1.251870844629331</v>
       </c>
     </row>
     <row r="42">
@@ -1891,28 +1891,28 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1966770500476557</v>
+        <v>0.2040927728987508</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1757571815593134</v>
+        <v>0.183366022192989</v>
       </c>
       <c r="F42" t="n">
-        <v>9.401447726942214</v>
+        <v>9.846829143461276</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>1044.160908794896</v>
+        <v>19.17140335428466</v>
       </c>
       <c r="I42" t="n">
-        <v>5309.012457436651</v>
+        <v>93.93474880071071</v>
       </c>
       <c r="J42" t="n">
-        <v>4.565004657665561</v>
+        <v>0.08824588406570433</v>
       </c>
       <c r="K42" t="n">
-        <v>1.261047676723929</v>
+        <v>1.248302553022435</v>
       </c>
     </row>
     <row r="43">
@@ -1926,28 +1926,28 @@
         <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1910186752401951</v>
+        <v>0.203317604977789</v>
       </c>
       <c r="E43" t="n">
-        <v>0.170381396547343</v>
+        <v>0.1829940744925285</v>
       </c>
       <c r="F43" t="n">
-        <v>9.256001146428064</v>
+        <v>10.00404949943337</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>1033.546991268666</v>
+        <v>19.3829390108378</v>
       </c>
       <c r="I43" t="n">
-        <v>5410.711753544724</v>
+        <v>95.33330383738904</v>
       </c>
       <c r="J43" t="n">
-        <v>4.412718370940306</v>
+        <v>0.08691105804591003</v>
       </c>
       <c r="K43" t="n">
-        <v>1.271504123092589</v>
+        <v>1.237533252696213</v>
       </c>
     </row>
     <row r="44">
@@ -1961,28 +1961,28 @@
         <v>207</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1899651345352251</v>
+        <v>0.2004356281944263</v>
       </c>
       <c r="E44" t="n">
-        <v>0.169815013503763</v>
+        <v>0.1805459672042379</v>
       </c>
       <c r="F44" t="n">
-        <v>9.427493474536295</v>
+        <v>10.07737780414164</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>1060.365810237205</v>
+        <v>19.45279392638352</v>
       </c>
       <c r="I44" t="n">
-        <v>5581.896977208637</v>
+        <v>97.05257544089891</v>
       </c>
       <c r="J44" t="n">
-        <v>4.482980887075856</v>
+        <v>0.08465624195505604</v>
       </c>
       <c r="K44" t="n">
-        <v>1.266462611156275</v>
+        <v>1.231254171188481</v>
       </c>
     </row>
     <row r="45">
@@ -1996,28 +1996,28 @@
         <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1944542017511583</v>
+        <v>0.1975086254272901</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1749021192693904</v>
+        <v>0.1780306794425156</v>
       </c>
       <c r="F45" t="n">
-        <v>9.945447086390088</v>
+        <v>10.14011567655431</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>1109.347921704105</v>
+        <v>19.48421262112608</v>
       </c>
       <c r="I45" t="n">
-        <v>5704.931607102682</v>
+        <v>98.6499327762215</v>
       </c>
       <c r="J45" t="n">
-        <v>4.604197772217456</v>
+        <v>0.08288993498466292</v>
       </c>
       <c r="K45" t="n">
-        <v>1.245890345526003</v>
+        <v>1.228866584940698</v>
       </c>
     </row>
     <row r="46">
@@ -2031,28 +2031,28 @@
         <v>216</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1870785774179005</v>
+        <v>0.1935411401699965</v>
       </c>
       <c r="E46" t="n">
-        <v>0.16772330545166</v>
+        <v>0.1743397387454726</v>
       </c>
       <c r="F46" t="n">
-        <v>9.665510138230218</v>
+        <v>10.07953200347174</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>1075.328205134731</v>
+        <v>19.35504710031574</v>
       </c>
       <c r="I46" t="n">
-        <v>5748.002897908714</v>
+        <v>100.0048211109807</v>
       </c>
       <c r="J46" t="n">
-        <v>4.388162878357412</v>
+        <v>0.08098208003205989</v>
       </c>
       <c r="K46" t="n">
-        <v>1.230585816827374</v>
+        <v>1.241155180706661</v>
       </c>
     </row>
     <row r="47">
@@ -2066,28 +2066,28 @@
         <v>221</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1874142986462786</v>
+        <v>0.1909033576557405</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1685169567543315</v>
+        <v>0.1720871566709902</v>
       </c>
       <c r="F47" t="n">
-        <v>9.917495260333098</v>
+        <v>10.14569082305509</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>1099.062136496783</v>
+        <v>19.52816867570249</v>
       </c>
       <c r="I47" t="n">
-        <v>5864.345167020192</v>
+        <v>102.2934793578539</v>
       </c>
       <c r="J47" t="n">
-        <v>4.402013526601429</v>
+        <v>0.07934641152414687</v>
       </c>
       <c r="K47" t="n">
-        <v>1.227025148049095</v>
+        <v>1.238004811282324</v>
       </c>
     </row>
     <row r="48">
@@ -2101,28 +2101,28 @@
         <v>226</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1854214466450858</v>
+        <v>0.1896799545498968</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1669082977052013</v>
+        <v>0.1712635898805763</v>
       </c>
       <c r="F48" t="n">
-        <v>10.0156622326749</v>
+        <v>10.29953294017256</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>1103.682521513988</v>
+        <v>19.65814997667698</v>
       </c>
       <c r="I48" t="n">
-        <v>5952.291611803357</v>
+        <v>103.6385211253609</v>
       </c>
       <c r="J48" t="n">
-        <v>4.298214931583274</v>
+        <v>0.07836696899390783</v>
       </c>
       <c r="K48" t="n">
-        <v>1.215975367667591</v>
+        <v>1.24120911180456</v>
       </c>
     </row>
     <row r="49">
@@ -2133,31 +2133,31 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1856235176696466</v>
+        <v>0.1820171650636473</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1676857096888018</v>
+        <v>0.1637586196409608</v>
       </c>
       <c r="F49" t="n">
-        <v>10.34817174249318</v>
+        <v>9.968875441604945</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>1136.107764509158</v>
+        <v>19.07097509156507</v>
       </c>
       <c r="I49" t="n">
-        <v>6120.49474534301</v>
+        <v>104.7756956597823</v>
       </c>
       <c r="J49" t="n">
-        <v>4.309345336910132</v>
+        <v>0.07486668404771867</v>
       </c>
       <c r="K49" t="n">
-        <v>1.221558912811017</v>
+        <v>1.215481887117924</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/MaxRel_Focus/tables/env_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/env_cutoff_metrics.xlsx
@@ -491,25 +491,25 @@
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>0.497229525129012</v>
+        <v>0.4762402806786764</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.005540949741976053</v>
+        <v>-0.04751943864264718</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9889791664011348</v>
+        <v>0.9092724451887563</v>
       </c>
       <c r="G2" t="n">
-        <v>0.517</v>
+        <v>0.586</v>
       </c>
       <c r="H2" t="n">
-        <v>2.565558931893026</v>
+        <v>152.739854869862</v>
       </c>
       <c r="I2" t="n">
-        <v>5.159707543970486</v>
+        <v>320.7201512904302</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2024257857693038</v>
+        <v>9.6197485725428</v>
       </c>
       <c r="K2" t="n">
         <v>9.499101272840637</v>
@@ -526,25 +526,25 @@
         <v>16</v>
       </c>
       <c r="D3" t="n">
-        <v>0.362683019842467</v>
+        <v>0.3738749459883865</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04402452976370064</v>
+        <v>0.06081241898257983</v>
       </c>
       <c r="F3" t="n">
-        <v>1.138155834959296</v>
+        <v>1.194250073824555</v>
       </c>
       <c r="G3" t="n">
-        <v>0.338</v>
+        <v>0.273</v>
       </c>
       <c r="H3" t="n">
-        <v>2.867092576922619</v>
+        <v>179.8211181722594</v>
       </c>
       <c r="I3" t="n">
-        <v>7.905229691116926</v>
+        <v>480.965948913424</v>
       </c>
       <c r="J3" t="n">
-        <v>0.1465055446309235</v>
+        <v>7.107951626641549</v>
       </c>
       <c r="K3" t="n">
         <v>5.805982957435718</v>
@@ -561,25 +561,25 @@
         <v>20</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2558352404892725</v>
+        <v>0.2854890483263509</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.009937887907415899</v>
+        <v>0.03030656558576172</v>
       </c>
       <c r="F4" t="n">
-        <v>0.962607627161679</v>
+        <v>1.118764286875329</v>
       </c>
       <c r="G4" t="n">
-        <v>0.506</v>
+        <v>0.342</v>
       </c>
       <c r="H4" t="n">
-        <v>2.6368237255011</v>
+        <v>168.6762768029946</v>
       </c>
       <c r="I4" t="n">
-        <v>10.3067260024784</v>
+        <v>590.8327404915924</v>
       </c>
       <c r="J4" t="n">
-        <v>0.09020054841811048</v>
+        <v>4.746203637589729</v>
       </c>
       <c r="K4" t="n">
         <v>3.76250275686638</v>
@@ -596,25 +596,25 @@
         <v>25</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2356343537906873</v>
+        <v>0.2734391046189723</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03448549952507873</v>
+        <v>0.08223886899238619</v>
       </c>
       <c r="F5" t="n">
-        <v>1.171442684329397</v>
+        <v>1.43011907764067</v>
       </c>
       <c r="G5" t="n">
-        <v>0.278</v>
+        <v>0.089</v>
       </c>
       <c r="H5" t="n">
-        <v>2.941528490386848</v>
+        <v>190.7421144106072</v>
       </c>
       <c r="I5" t="n">
-        <v>12.48344497763595</v>
+        <v>697.5670677257358</v>
       </c>
       <c r="J5" t="n">
-        <v>0.07449769443232448</v>
+        <v>4.135758622862749</v>
       </c>
       <c r="K5" t="n">
         <v>3.453666067834401</v>
@@ -631,25 +631,25 @@
         <v>30</v>
       </c>
       <c r="D6" t="n">
-        <v>0.202966683733261</v>
+        <v>0.2095356093814405</v>
       </c>
       <c r="E6" t="n">
-        <v>0.03691807617769038</v>
+        <v>0.04485552800257397</v>
       </c>
       <c r="F6" t="n">
-        <v>1.222332946485776</v>
+        <v>1.272379802262657</v>
       </c>
       <c r="G6" t="n">
-        <v>0.242</v>
+        <v>0.153</v>
       </c>
       <c r="H6" t="n">
-        <v>2.935322066650834</v>
+        <v>169.5298412706895</v>
       </c>
       <c r="I6" t="n">
-        <v>14.46208812530256</v>
+        <v>809.0741319394349</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06762898153473279</v>
+        <v>3.015643630577912</v>
       </c>
       <c r="K6" t="n">
         <v>2.138005127264277</v>
@@ -666,25 +666,25 @@
         <v>34</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2155392725494269</v>
+        <v>0.2276565958284196</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07545699979039588</v>
+        <v>0.08973813079778015</v>
       </c>
       <c r="F7" t="n">
-        <v>1.538662018428248</v>
+        <v>1.650660742039468</v>
       </c>
       <c r="G7" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.029</v>
       </c>
       <c r="H7" t="n">
-        <v>3.537904715154093</v>
+        <v>210.6635293122477</v>
       </c>
       <c r="I7" t="n">
-        <v>16.41419994280991</v>
+        <v>925.3565816780495</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07852123067006236</v>
+        <v>3.944363245906707</v>
       </c>
       <c r="K7" t="n">
         <v>2.07152114076263</v>
@@ -701,25 +701,25 @@
         <v>39</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2406614020034559</v>
+        <v>0.2549791396600926</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1256100992767067</v>
+        <v>0.1420971911237429</v>
       </c>
       <c r="F8" t="n">
-        <v>2.091774680509572</v>
+        <v>2.258812351896863</v>
       </c>
       <c r="G8" t="n">
-        <v>0.007</v>
+        <v>0.002</v>
       </c>
       <c r="H8" t="n">
-        <v>4.546080817089507</v>
+        <v>274.3051486143099</v>
       </c>
       <c r="I8" t="n">
-        <v>18.88994570481321</v>
+        <v>1075.794470794671</v>
       </c>
       <c r="J8" t="n">
-        <v>0.08201465976108782</v>
+        <v>4.15741950280689</v>
       </c>
       <c r="K8" t="n">
         <v>1.747340313866239</v>
@@ -736,25 +736,25 @@
         <v>44</v>
       </c>
       <c r="D9" t="n">
-        <v>0.227504156184188</v>
+        <v>0.2414387621300756</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1258599662084232</v>
+        <v>0.1416280729366645</v>
       </c>
       <c r="F9" t="n">
-        <v>2.238240633708944</v>
+        <v>2.418966987215371</v>
       </c>
       <c r="G9" t="n">
-        <v>0.007</v>
+        <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>4.705756602424207</v>
+        <v>290.2831459440172</v>
       </c>
       <c r="I9" t="n">
-        <v>20.6842665266054</v>
+        <v>1202.305476481969</v>
       </c>
       <c r="J9" t="n">
-        <v>0.07561571516162249</v>
+        <v>4.054506171080378</v>
       </c>
       <c r="K9" t="n">
         <v>1.638443591008128</v>
@@ -771,25 +771,25 @@
         <v>48</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2461834002386351</v>
+        <v>0.2496937919764782</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1564433288384726</v>
+        <v>0.1603716243546304</v>
       </c>
       <c r="F10" t="n">
-        <v>2.743294008992612</v>
+        <v>2.795429159686045</v>
       </c>
       <c r="G10" t="n">
         <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>5.612214642086499</v>
+        <v>328.2714833978465</v>
       </c>
       <c r="I10" t="n">
-        <v>22.7968849103813</v>
+        <v>1314.696215710363</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08931103097109075</v>
+        <v>4.818207844548787</v>
       </c>
       <c r="K10" t="n">
         <v>1.508631271790515</v>
@@ -806,25 +806,25 @@
         <v>53</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2020004161205684</v>
+        <v>0.214687990234689</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1171068433674374</v>
+        <v>0.131144159408592</v>
       </c>
       <c r="F11" t="n">
-        <v>2.379454764001769</v>
+        <v>2.569764734413233</v>
       </c>
       <c r="G11" t="n">
-        <v>0.003</v>
+        <v>0.002</v>
       </c>
       <c r="H11" t="n">
-        <v>4.976230906224685</v>
+        <v>304.9405606050854</v>
       </c>
       <c r="I11" t="n">
-        <v>24.63475571879274</v>
+        <v>1420.389469721784</v>
       </c>
       <c r="J11" t="n">
-        <v>0.06763969625822487</v>
+        <v>3.904954691843019</v>
       </c>
       <c r="K11" t="n">
         <v>1.198096996920468</v>
@@ -841,25 +841,25 @@
         <v>58</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2072009476532409</v>
+        <v>0.2110129821777128</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1309702695429755</v>
+        <v>0.1351488458486466</v>
       </c>
       <c r="F12" t="n">
-        <v>2.718078243427549</v>
+        <v>2.781458965833725</v>
       </c>
       <c r="G12" t="n">
         <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>5.755195414681758</v>
+        <v>334.6043940039855</v>
       </c>
       <c r="I12" t="n">
-        <v>27.77591260978839</v>
+        <v>1585.705251642694</v>
       </c>
       <c r="J12" t="n">
-        <v>0.06926089161108721</v>
+        <v>3.910343769355727</v>
       </c>
       <c r="K12" t="n">
         <v>1.192142318651783</v>
@@ -876,25 +876,25 @@
         <v>62</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1956147144569446</v>
+        <v>0.2012329385243729</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1237945996763147</v>
+        <v>0.1299144508926207</v>
       </c>
       <c r="F13" t="n">
-        <v>2.723675881811628</v>
+        <v>2.821609728510003</v>
       </c>
       <c r="G13" t="n">
         <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>5.678981192679139</v>
+        <v>333.3328444039503</v>
       </c>
       <c r="I13" t="n">
-        <v>29.03146222125893</v>
+        <v>1656.452700279869</v>
       </c>
       <c r="J13" t="n">
-        <v>0.06462539201775121</v>
+        <v>3.52811701831622</v>
       </c>
       <c r="K13" t="n">
         <v>1.202788401670979</v>
@@ -911,25 +911,25 @@
         <v>67</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1958287236647548</v>
+        <v>0.1937500757338941</v>
       </c>
       <c r="E14" t="n">
-        <v>0.12991304527662</v>
+        <v>0.1276640163678198</v>
       </c>
       <c r="F14" t="n">
-        <v>2.970897492879402</v>
+        <v>2.931784367118083</v>
       </c>
       <c r="G14" t="n">
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>5.885261041146888</v>
+        <v>337.335698279449</v>
       </c>
       <c r="I14" t="n">
-        <v>30.05310421785747</v>
+        <v>1741.086794426664</v>
       </c>
       <c r="J14" t="n">
-        <v>0.06283596132881994</v>
+        <v>3.352202975917723</v>
       </c>
       <c r="K14" t="n">
         <v>1.192628746553563</v>
@@ -946,25 +946,25 @@
         <v>72</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1584090861729938</v>
+        <v>0.1741406219907763</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09465219876185693</v>
+        <v>0.1115755175961382</v>
       </c>
       <c r="F15" t="n">
-        <v>2.484579981947541</v>
+        <v>2.783350618139465</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>4.961027298884605</v>
+        <v>318.0656916783984</v>
       </c>
       <c r="I15" t="n">
-        <v>31.31782032671293</v>
+        <v>1826.487628459518</v>
       </c>
       <c r="J15" t="n">
-        <v>0.04839043811674677</v>
+        <v>2.90930359930131</v>
       </c>
       <c r="K15" t="n">
         <v>1.205088974378534</v>
@@ -981,25 +981,25 @@
         <v>76</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1712383201715743</v>
+        <v>0.1719666503070997</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1120410573266869</v>
+        <v>0.1128214110433211</v>
       </c>
       <c r="F16" t="n">
-        <v>2.892672936927233</v>
+        <v>2.907531568858063</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>5.731630851746091</v>
+        <v>332.5627216759184</v>
       </c>
       <c r="I16" t="n">
-        <v>33.47166011674965</v>
+        <v>1933.879162512177</v>
       </c>
       <c r="J16" t="n">
-        <v>0.05504833728506429</v>
+        <v>3.092673042853001</v>
       </c>
       <c r="K16" t="n">
         <v>1.235848094617273</v>
@@ -1016,25 +1016,25 @@
         <v>81</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1615294040545064</v>
+        <v>0.162957108944356</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1056313643248068</v>
+        <v>0.1071542495406465</v>
       </c>
       <c r="F17" t="n">
-        <v>2.889715003166437</v>
+        <v>2.920228652898083</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>5.666659808775734</v>
+        <v>330.4203394156357</v>
       </c>
       <c r="I17" t="n">
-        <v>35.08128963853281</v>
+        <v>2027.652193611648</v>
       </c>
       <c r="J17" t="n">
-        <v>0.05117394519578227</v>
+        <v>2.871105600591837</v>
       </c>
       <c r="K17" t="n">
         <v>1.238102230181861</v>
@@ -1051,25 +1051,25 @@
         <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1449374684574826</v>
+        <v>0.1449075027891034</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09149606023607526</v>
+        <v>0.09146422171342228</v>
       </c>
       <c r="F18" t="n">
-        <v>2.712081759840755</v>
+        <v>2.711426017873038</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>5.498014450622271</v>
+        <v>318.7916334033819</v>
       </c>
       <c r="I18" t="n">
-        <v>37.93370002343538</v>
+        <v>2199.966373496529</v>
       </c>
       <c r="J18" t="n">
-        <v>0.04833282094224045</v>
+        <v>2.70931798289423</v>
       </c>
       <c r="K18" t="n">
         <v>1.256619408695372</v>
@@ -1086,25 +1086,25 @@
         <v>90</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1422528615963377</v>
+        <v>0.1415973452455589</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09119648431040539</v>
+        <v>0.09050194912922316</v>
       </c>
       <c r="F19" t="n">
-        <v>2.786191836519765</v>
+        <v>2.771234905844846</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>5.526071485582287</v>
+        <v>318.4578732463511</v>
       </c>
       <c r="I19" t="n">
-        <v>38.84682124190434</v>
+        <v>2249.038445558988</v>
       </c>
       <c r="J19" t="n">
-        <v>0.04737344038262722</v>
+        <v>2.630496794718149</v>
       </c>
       <c r="K19" t="n">
         <v>1.215104032616906</v>
@@ -1121,25 +1121,25 @@
         <v>95</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1752041438020825</v>
+        <v>0.1752744235758737</v>
       </c>
       <c r="E20" t="n">
-        <v>0.128867297948267</v>
+        <v>0.1289415260239566</v>
       </c>
       <c r="F20" t="n">
-        <v>3.781097754362048</v>
+        <v>3.782936808117261</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>7.527032471112671</v>
+        <v>440.1446200890451</v>
       </c>
       <c r="I20" t="n">
-        <v>42.96149798611786</v>
+        <v>2511.174255258714</v>
       </c>
       <c r="J20" t="n">
-        <v>0.06704050156586738</v>
+        <v>3.816690313760467</v>
       </c>
       <c r="K20" t="n">
         <v>1.247082934141258</v>
@@ -1156,25 +1156,25 @@
         <v>100</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1749839917670264</v>
+        <v>0.1737900241634167</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1311001615418683</v>
+        <v>0.129842685023173</v>
       </c>
       <c r="F21" t="n">
-        <v>3.987436622309915</v>
+        <v>3.954506178606667</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>7.878211222635999</v>
+        <v>460.4858034505552</v>
       </c>
       <c r="I21" t="n">
-        <v>45.02246830170068</v>
+        <v>2649.667641553207</v>
       </c>
       <c r="J21" t="n">
-        <v>0.06492950275632782</v>
+        <v>3.74272018832005</v>
       </c>
       <c r="K21" t="n">
         <v>1.24199407636883</v>
@@ -1191,25 +1191,25 @@
         <v>104</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1600180586269882</v>
+        <v>0.1648354030519697</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1171618371283651</v>
+        <v>0.1222249644321723</v>
       </c>
       <c r="F22" t="n">
-        <v>3.733834972645207</v>
+        <v>3.868427746608191</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>7.487263008734812</v>
+        <v>453.9206353469609</v>
       </c>
       <c r="I22" t="n">
-        <v>46.79011277213453</v>
+        <v>2753.781208056667</v>
       </c>
       <c r="J22" t="n">
-        <v>0.05992674953692851</v>
+        <v>3.574642843533844</v>
       </c>
       <c r="K22" t="n">
         <v>1.234102768844652</v>
@@ -1226,25 +1226,25 @@
         <v>109</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1544569110394849</v>
+        <v>0.1636721350722362</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1134111300219842</v>
+        <v>0.1230736950271991</v>
       </c>
       <c r="F23" t="n">
-        <v>3.763039884017044</v>
+        <v>4.031488276167008</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>7.556120648359236</v>
+        <v>473.1488443023533</v>
       </c>
       <c r="I23" t="n">
-        <v>48.92057336578231</v>
+        <v>2890.833214178641</v>
       </c>
       <c r="J23" t="n">
-        <v>0.05796578752922536</v>
+        <v>3.51431928430009</v>
       </c>
       <c r="K23" t="n">
         <v>1.206044823933059</v>
@@ -1261,25 +1261,25 @@
         <v>114</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1523015830061783</v>
+        <v>0.1620526385650938</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1130562859231311</v>
+        <v>0.1232587792394036</v>
       </c>
       <c r="F24" t="n">
-        <v>3.880760099328377</v>
+        <v>4.177275511688499</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>7.874687210458195</v>
+        <v>494.1833339814851</v>
       </c>
       <c r="I24" t="n">
-        <v>51.70456573743391</v>
+        <v>3049.523527399895</v>
       </c>
       <c r="J24" t="n">
-        <v>0.05766099161477416</v>
+        <v>3.524583968488105</v>
       </c>
       <c r="K24" t="n">
         <v>1.216477571429641</v>
@@ -1296,25 +1296,25 @@
         <v>118</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1587769292215391</v>
+        <v>0.1695281575767169</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1212223278475006</v>
+        <v>0.1324535217542488</v>
       </c>
       <c r="F25" t="n">
-        <v>4.22789547518142</v>
+        <v>4.572618282442556</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>8.632978520192564</v>
+        <v>541.0020996052117</v>
       </c>
       <c r="I25" t="n">
-        <v>54.37174382020638</v>
+        <v>3191.22266966413</v>
       </c>
       <c r="J25" t="n">
-        <v>0.06215791494785122</v>
+        <v>3.806263917930259</v>
       </c>
       <c r="K25" t="n">
         <v>1.225943713504539</v>
@@ -1331,25 +1331,25 @@
         <v>123</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1561463138065758</v>
+        <v>0.1670347805709292</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1200841904649764</v>
+        <v>0.1314379763218236</v>
       </c>
       <c r="F26" t="n">
-        <v>4.329925676518717</v>
+        <v>4.692409447826377</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>8.752251075143983</v>
+        <v>550.4857270068483</v>
       </c>
       <c r="I26" t="n">
-        <v>56.05160225546993</v>
+        <v>3295.635346873709</v>
       </c>
       <c r="J26" t="n">
-        <v>0.06044080359204083</v>
+        <v>3.702873691781363</v>
       </c>
       <c r="K26" t="n">
         <v>1.227326111231638</v>
@@ -1366,25 +1366,25 @@
         <v>128</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1629936691051306</v>
+        <v>0.1714399604439396</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1286901309537015</v>
+        <v>0.1374825817736093</v>
       </c>
       <c r="F27" t="n">
-        <v>4.751511881532847</v>
+        <v>5.048680644885354</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>9.702957258828125</v>
+        <v>597.5314478875126</v>
       </c>
       <c r="I27" t="n">
-        <v>59.52965726889514</v>
+        <v>3485.368559000011</v>
       </c>
       <c r="J27" t="n">
-        <v>0.06513888145763021</v>
+        <v>3.92203726686862</v>
       </c>
       <c r="K27" t="n">
         <v>1.256179197144718</v>
@@ -1401,25 +1401,25 @@
         <v>132</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1633653691685864</v>
+        <v>0.1728618006413</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1301655822308319</v>
+        <v>0.1400388562223039</v>
       </c>
       <c r="F28" t="n">
-        <v>4.920675228274095</v>
+        <v>5.266492805601487</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>9.97588831769793</v>
+        <v>613.248072123656</v>
       </c>
       <c r="I28" t="n">
-        <v>61.06489012003038</v>
+        <v>3547.620526041999</v>
       </c>
       <c r="J28" t="n">
-        <v>0.06534494031331908</v>
+        <v>3.901711705248414</v>
       </c>
       <c r="K28" t="n">
         <v>1.232262433822034</v>
@@ -1436,25 +1436,25 @@
         <v>137</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1764342253371078</v>
+        <v>0.1851706532066572</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1450004171438677</v>
+        <v>0.1540702964588196</v>
       </c>
       <c r="F29" t="n">
-        <v>5.61288101818506</v>
+        <v>5.953971998071453</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>11.23362432134531</v>
+        <v>681.036076629953</v>
       </c>
       <c r="I29" t="n">
-        <v>63.67032416687606</v>
+        <v>3677.883427185905</v>
       </c>
       <c r="J29" t="n">
-        <v>0.0710576490797504</v>
+        <v>4.214565622679459</v>
       </c>
       <c r="K29" t="n">
         <v>1.279991572266424</v>
@@ -1471,25 +1471,25 @@
         <v>142</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1921549516849918</v>
+        <v>0.1952274777393943</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1624547660851753</v>
+        <v>0.1656402526562837</v>
       </c>
       <c r="F30" t="n">
-        <v>6.469823262187936</v>
+        <v>6.598370654598407</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>12.77490667020447</v>
+        <v>743.0337669506551</v>
       </c>
       <c r="I30" t="n">
-        <v>66.48231834871964</v>
+        <v>3805.989687284276</v>
       </c>
       <c r="J30" t="n">
-        <v>0.07970906715472528</v>
+        <v>4.490824554866782</v>
       </c>
       <c r="K30" t="n">
         <v>1.295766298011334</v>
@@ -1506,25 +1506,25 @@
         <v>146</v>
       </c>
       <c r="D31" t="n">
-        <v>0.188083657457276</v>
+        <v>0.1944590370301058</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1590866452236073</v>
+        <v>0.1656897169240381</v>
       </c>
       <c r="F31" t="n">
-        <v>6.486311622094993</v>
+        <v>6.759250351178545</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>12.94796616613969</v>
+        <v>754.709106785005</v>
       </c>
       <c r="I31" t="n">
-        <v>68.84152690980542</v>
+        <v>3881.069855694917</v>
       </c>
       <c r="J31" t="n">
-        <v>0.07844337514611927</v>
+        <v>4.432548524502447</v>
       </c>
       <c r="K31" t="n">
         <v>1.272049585058742</v>
@@ -1541,25 +1541,25 @@
         <v>151</v>
       </c>
       <c r="D32" t="n">
-        <v>0.18792162834294</v>
+        <v>0.1996244098306212</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1599189258720067</v>
+        <v>0.1720252515489183</v>
       </c>
       <c r="F32" t="n">
-        <v>6.710839017698497</v>
+        <v>7.232989056878782</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>13.35601619833081</v>
+        <v>801.1225415244805</v>
       </c>
       <c r="I32" t="n">
-        <v>71.07226728557976</v>
+        <v>4013.149204569837</v>
       </c>
       <c r="J32" t="n">
-        <v>0.07832950725569948</v>
+        <v>4.578095034724645</v>
       </c>
       <c r="K32" t="n">
         <v>1.27129152495296</v>
@@ -1576,25 +1576,25 @@
         <v>156</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1872152835215359</v>
+        <v>0.2030297983472427</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1601224596389202</v>
+        <v>0.1764641249588174</v>
       </c>
       <c r="F33" t="n">
-        <v>6.910142860437131</v>
+        <v>7.642561714084145</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>13.87964955332536</v>
+        <v>848.4257865479465</v>
       </c>
       <c r="I33" t="n">
-        <v>74.13737432248017</v>
+        <v>4178.823963056301</v>
       </c>
       <c r="J33" t="n">
-        <v>0.07981280278600013</v>
+        <v>4.740429674420225</v>
       </c>
       <c r="K33" t="n">
         <v>1.286237448189681</v>
@@ -1611,25 +1611,25 @@
         <v>160</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1844163686913182</v>
+        <v>0.2016068103968351</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1579363806618156</v>
+        <v>0.1756849535915376</v>
       </c>
       <c r="F34" t="n">
-        <v>6.964367524858807</v>
+        <v>7.7774833767168</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>13.96348312012855</v>
+        <v>860.9921103988788</v>
       </c>
       <c r="I34" t="n">
-        <v>75.71715688373116</v>
+        <v>4270.649928462908</v>
       </c>
       <c r="J34" t="n">
-        <v>0.07812895568695974</v>
+        <v>4.689116319364187</v>
       </c>
       <c r="K34" t="n">
         <v>1.289054894447494</v>
@@ -1646,25 +1646,25 @@
         <v>165</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1863159022706069</v>
+        <v>0.1984574683180557</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1607283520275442</v>
+        <v>0.1732517283280575</v>
       </c>
       <c r="F35" t="n">
-        <v>7.28150606450186</v>
+        <v>7.873502955945929</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>14.58647520795661</v>
+        <v>882.6317293133003</v>
       </c>
       <c r="I35" t="n">
-        <v>78.28894383245442</v>
+        <v>4447.460389340251</v>
       </c>
       <c r="J35" t="n">
-        <v>0.07861916684670875</v>
+        <v>4.642283505336225</v>
       </c>
       <c r="K35" t="n">
         <v>1.29801977536493</v>
@@ -1681,25 +1681,25 @@
         <v>170</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1770374342736645</v>
+        <v>0.1886433320083733</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1519471121478615</v>
+        <v>0.1639068482281408</v>
       </c>
       <c r="F36" t="n">
-        <v>7.056004836685577</v>
+        <v>7.626117506608693</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>14.30171721474321</v>
+        <v>862.9878275018511</v>
       </c>
       <c r="I36" t="n">
-        <v>80.78357706334363</v>
+        <v>4574.706236971821</v>
       </c>
       <c r="J36" t="n">
-        <v>0.07501146775061275</v>
+        <v>4.385826029648479</v>
       </c>
       <c r="K36" t="n">
         <v>1.291723506782565</v>
@@ -1716,25 +1716,25 @@
         <v>174</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1845319601544374</v>
+        <v>0.1914581169261083</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1602620780161766</v>
+        <v>0.1673943704060521</v>
       </c>
       <c r="F37" t="n">
-        <v>7.603331532604684</v>
+        <v>7.956288800105778</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>15.3551387832189</v>
+        <v>904.7763053110104</v>
       </c>
       <c r="I37" t="n">
-        <v>83.21127012560841</v>
+        <v>4725.714009086392</v>
       </c>
       <c r="J37" t="n">
-        <v>0.07972411141048599</v>
+        <v>4.595013398872279</v>
       </c>
       <c r="K37" t="n">
         <v>1.289824679652318</v>
@@ -1751,25 +1751,25 @@
         <v>179</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1976598587505477</v>
+        <v>0.1995589659622045</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1744708373271531</v>
+        <v>0.1764248320304763</v>
       </c>
       <c r="F38" t="n">
-        <v>8.523855109777754</v>
+        <v>8.626169734779298</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>17.04592170097868</v>
+        <v>973.7267267372756</v>
       </c>
       <c r="I38" t="n">
-        <v>86.23866175322485</v>
+        <v>4879.393526832037</v>
       </c>
       <c r="J38" t="n">
-        <v>0.08678708197962093</v>
+        <v>4.842942421052491</v>
       </c>
       <c r="K38" t="n">
         <v>1.266444647511108</v>
@@ -1786,25 +1786,25 @@
         <v>184</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1943875202304184</v>
+        <v>0.1966699063350408</v>
       </c>
       <c r="E39" t="n">
-        <v>0.171757956191947</v>
+        <v>0.1741044542658003</v>
       </c>
       <c r="F39" t="n">
-        <v>8.589980783542709</v>
+        <v>8.715531411982072</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>17.16264204753859</v>
+        <v>983.1318146203869</v>
       </c>
       <c r="I39" t="n">
-        <v>88.29086366858712</v>
+        <v>4998.892982363828</v>
       </c>
       <c r="J39" t="n">
-        <v>0.08560830941369901</v>
+        <v>4.769070289625432</v>
       </c>
       <c r="K39" t="n">
         <v>1.249385797859496</v>
@@ -1821,25 +1821,25 @@
         <v>188</v>
       </c>
       <c r="D40" t="n">
-        <v>0.2072824330432303</v>
+        <v>0.213374764181171</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1855044779070555</v>
+        <v>0.1917641807795548</v>
       </c>
       <c r="F40" t="n">
-        <v>9.517993390431638</v>
+        <v>9.873623502696063</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>18.89673452555497</v>
+        <v>1103.829986324791</v>
       </c>
       <c r="I40" t="n">
-        <v>91.16418718229689</v>
+        <v>5173.198389044535</v>
       </c>
       <c r="J40" t="n">
-        <v>0.09186230640978409</v>
+        <v>5.293940708486262</v>
       </c>
       <c r="K40" t="n">
         <v>1.261837441994162</v>
@@ -1856,25 +1856,25 @@
         <v>193</v>
       </c>
       <c r="D41" t="n">
-        <v>0.206225208488714</v>
+        <v>0.2097908305039086</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1850012835819951</v>
+        <v>0.1886622430842269</v>
       </c>
       <c r="F41" t="n">
-        <v>9.716638623397559</v>
+        <v>9.929240717175698</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>19.12463638290981</v>
+        <v>1107.674704161637</v>
       </c>
       <c r="I41" t="n">
-        <v>92.73665679895012</v>
+        <v>5279.900468009256</v>
       </c>
       <c r="J41" t="n">
-        <v>0.08990168774592108</v>
+        <v>5.116677894729317</v>
       </c>
       <c r="K41" t="n">
         <v>1.251870844629331</v>
@@ -1891,25 +1891,25 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2040927728987508</v>
+        <v>0.2085799036064721</v>
       </c>
       <c r="E42" t="n">
-        <v>0.183366022192989</v>
+        <v>0.1879700052628905</v>
       </c>
       <c r="F42" t="n">
-        <v>9.846829143461276</v>
+        <v>10.12037517746564</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>19.17140335428466</v>
+        <v>1114.138359256528</v>
       </c>
       <c r="I42" t="n">
-        <v>93.93474880071071</v>
+        <v>5341.542209927255</v>
       </c>
       <c r="J42" t="n">
-        <v>0.08824588406570433</v>
+        <v>5.024790342344003</v>
       </c>
       <c r="K42" t="n">
         <v>1.248302553022435</v>
@@ -1926,25 +1926,25 @@
         <v>202</v>
       </c>
       <c r="D43" t="n">
-        <v>0.203317604977789</v>
+        <v>0.2077291735271049</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1829940744925285</v>
+        <v>0.1875181830558575</v>
       </c>
       <c r="F43" t="n">
-        <v>10.00404949943337</v>
+        <v>10.27803035297185</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>19.3829390108378</v>
+        <v>1126.347440984499</v>
       </c>
       <c r="I43" t="n">
-        <v>95.33330383738904</v>
+        <v>5422.191894666788</v>
       </c>
       <c r="J43" t="n">
-        <v>0.08691105804591003</v>
+        <v>4.956904069916598</v>
       </c>
       <c r="K43" t="n">
         <v>1.237533252696213</v>
@@ -1961,25 +1961,25 @@
         <v>207</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2004356281944263</v>
+        <v>0.2051605000095512</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1805459672042379</v>
+        <v>0.1853883731441172</v>
       </c>
       <c r="F44" t="n">
-        <v>10.07737780414164</v>
+        <v>10.37624841302309</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>19.45279392638352</v>
+        <v>1134.366338289732</v>
       </c>
       <c r="I44" t="n">
-        <v>97.05257544089891</v>
+        <v>5529.165400927186</v>
       </c>
       <c r="J44" t="n">
-        <v>0.08465624195505604</v>
+        <v>4.854284703604523</v>
       </c>
       <c r="K44" t="n">
         <v>1.231254171188481</v>
@@ -1996,25 +1996,25 @@
         <v>212</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1975086254272901</v>
+        <v>0.205761826316596</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1780306794425156</v>
+        <v>0.1864842007417561</v>
       </c>
       <c r="F45" t="n">
-        <v>10.14011567655431</v>
+        <v>10.67360840253818</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>19.48421262112608</v>
+        <v>1165.823274156873</v>
       </c>
       <c r="I45" t="n">
-        <v>98.6499327762215</v>
+        <v>5665.887084240181</v>
       </c>
       <c r="J45" t="n">
-        <v>0.08288993498466292</v>
+        <v>4.871063128610766</v>
       </c>
       <c r="K45" t="n">
         <v>1.228866584940698</v>
@@ -2031,25 +2031,25 @@
         <v>216</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1935411401699965</v>
+        <v>0.200174201909983</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1743397387454726</v>
+        <v>0.1811307305268874</v>
       </c>
       <c r="F46" t="n">
-        <v>10.07953200347174</v>
+        <v>10.51143449023018</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>19.35504710031574</v>
+        <v>1153.77457530019</v>
       </c>
       <c r="I46" t="n">
-        <v>100.0048211109807</v>
+        <v>5763.852505923987</v>
       </c>
       <c r="J46" t="n">
-        <v>0.08098208003205989</v>
+        <v>4.745498337303298</v>
       </c>
       <c r="K46" t="n">
         <v>1.241155180706661</v>
@@ -2066,25 +2066,25 @@
         <v>221</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1909033576557405</v>
+        <v>0.1976571646801889</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1720871566709902</v>
+        <v>0.178998028975077</v>
       </c>
       <c r="F47" t="n">
-        <v>10.14569082305509</v>
+        <v>10.59305038582459</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>19.52816867570249</v>
+        <v>1163.307928747255</v>
       </c>
       <c r="I47" t="n">
-        <v>102.2934793578539</v>
+        <v>5885.483233706697</v>
       </c>
       <c r="J47" t="n">
-        <v>0.07934641152414687</v>
+        <v>4.657210249260886</v>
       </c>
       <c r="K47" t="n">
         <v>1.238004811282324</v>
@@ -2101,25 +2101,25 @@
         <v>226</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1896799545498968</v>
+        <v>0.1964605135409024</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1712635898805763</v>
+        <v>0.1781982524850138</v>
       </c>
       <c r="F48" t="n">
-        <v>10.29953294017256</v>
+        <v>10.75773218549816</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>19.65814997667698</v>
+        <v>1177.735270782045</v>
       </c>
       <c r="I48" t="n">
-        <v>103.6385211253609</v>
+        <v>5994.768361108068</v>
       </c>
       <c r="J48" t="n">
-        <v>0.07836696899390783</v>
+        <v>4.60820141700981</v>
       </c>
       <c r="K48" t="n">
         <v>1.24120911180456</v>
@@ -2136,25 +2136,25 @@
         <v>230</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1820171650636473</v>
+        <v>0.1878631183541706</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1637586196409608</v>
+        <v>0.1697350629602904</v>
       </c>
       <c r="F49" t="n">
-        <v>9.968875441604945</v>
+        <v>10.36311475623534</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>19.07097509156507</v>
+        <v>1137.955102989095</v>
       </c>
       <c r="I49" t="n">
-        <v>104.7756956597823</v>
+        <v>6057.363004289939</v>
       </c>
       <c r="J49" t="n">
-        <v>0.07486668404771867</v>
+        <v>4.377443629440397</v>
       </c>
       <c r="K49" t="n">
         <v>1.215481887117924</v>

--- a/results/01_pollution_assessment/MaxRel_Focus/tables/env_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/env_cutoff_metrics.xlsx
@@ -488,31 +488,31 @@
         <v>0.05</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.4762402806786764</v>
+        <v>0.406802307573177</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.04751943864264718</v>
+        <v>0.07724803400271985</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9092724451887563</v>
+        <v>1.234401554456567</v>
       </c>
       <c r="G2" t="n">
-        <v>0.586</v>
+        <v>0.245</v>
       </c>
       <c r="H2" t="n">
-        <v>152.739854869862</v>
+        <v>127.237518351049</v>
       </c>
       <c r="I2" t="n">
-        <v>320.7201512904302</v>
+        <v>312.7748195680061</v>
       </c>
       <c r="J2" t="n">
-        <v>9.6197485725428</v>
+        <v>5.337160403342086</v>
       </c>
       <c r="K2" t="n">
-        <v>9.499101272840637</v>
+        <v>2.276437896043347</v>
       </c>
     </row>
     <row r="3">
@@ -523,31 +523,31 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3738749459883865</v>
+        <v>0.3362461829828328</v>
       </c>
       <c r="E3" t="n">
-        <v>0.06081241898257983</v>
+        <v>0.1149949106437771</v>
       </c>
       <c r="F3" t="n">
-        <v>1.194250073824555</v>
+        <v>1.519748019652305</v>
       </c>
       <c r="G3" t="n">
-        <v>0.273</v>
+        <v>0.078</v>
       </c>
       <c r="H3" t="n">
-        <v>179.8211181722594</v>
+        <v>150.9542528172882</v>
       </c>
       <c r="I3" t="n">
-        <v>480.965948913424</v>
+        <v>448.9396771085287</v>
       </c>
       <c r="J3" t="n">
-        <v>7.107951626641549</v>
+        <v>5.615759696666783</v>
       </c>
       <c r="K3" t="n">
-        <v>5.805982957435718</v>
+        <v>1.969355397075732</v>
       </c>
     </row>
     <row r="4">
@@ -558,31 +558,31 @@
         <v>0.09</v>
       </c>
       <c r="C4" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2854890483263509</v>
+        <v>0.2972891958586353</v>
       </c>
       <c r="E4" t="n">
-        <v>0.03030656558576172</v>
+        <v>0.1299770996345009</v>
       </c>
       <c r="F4" t="n">
-        <v>1.118764286875329</v>
+        <v>1.776854169948246</v>
       </c>
       <c r="G4" t="n">
-        <v>0.342</v>
+        <v>0.021</v>
       </c>
       <c r="H4" t="n">
-        <v>168.6762768029946</v>
+        <v>162.0941288826627</v>
       </c>
       <c r="I4" t="n">
-        <v>590.8327404915924</v>
+        <v>545.2405642071851</v>
       </c>
       <c r="J4" t="n">
-        <v>4.746203637589729</v>
+        <v>4.268304743002249</v>
       </c>
       <c r="K4" t="n">
-        <v>3.76250275686638</v>
+        <v>1.697080486963792</v>
       </c>
     </row>
     <row r="5">
@@ -593,31 +593,31 @@
         <v>0.11</v>
       </c>
       <c r="C5" t="n">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2734391046189723</v>
+        <v>0.2818430561873084</v>
       </c>
       <c r="E5" t="n">
-        <v>0.08223886899238619</v>
+        <v>0.1536007447921849</v>
       </c>
       <c r="F5" t="n">
-        <v>1.43011907764067</v>
+        <v>2.197738430641119</v>
       </c>
       <c r="G5" t="n">
-        <v>0.089</v>
+        <v>0.007</v>
       </c>
       <c r="H5" t="n">
-        <v>190.7421144106072</v>
+        <v>217.3020114734366</v>
       </c>
       <c r="I5" t="n">
-        <v>697.5670677257358</v>
+        <v>771.0036018379717</v>
       </c>
       <c r="J5" t="n">
-        <v>4.135758622862749</v>
+        <v>4.560333544169722</v>
       </c>
       <c r="K5" t="n">
-        <v>3.453666067834401</v>
+        <v>1.83573103428303</v>
       </c>
     </row>
     <row r="6">
@@ -628,31 +628,31 @@
         <v>0.13</v>
       </c>
       <c r="C6" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2095356093814405</v>
+        <v>0.2652850961007155</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04485552800257397</v>
+        <v>0.1572387867037619</v>
       </c>
       <c r="F6" t="n">
-        <v>1.272379802262657</v>
+        <v>2.455290676575347</v>
       </c>
       <c r="G6" t="n">
-        <v>0.153</v>
+        <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>169.5298412706895</v>
+        <v>247.5942679300839</v>
       </c>
       <c r="I6" t="n">
-        <v>809.0741319394349</v>
+        <v>933.3139010420878</v>
       </c>
       <c r="J6" t="n">
-        <v>3.015643630577912</v>
+        <v>4.898487553407015</v>
       </c>
       <c r="K6" t="n">
-        <v>2.138005127264277</v>
+        <v>1.696756438349829</v>
       </c>
     </row>
     <row r="7">
@@ -663,31 +663,31 @@
         <v>0.15</v>
       </c>
       <c r="C7" t="n">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2276565958284196</v>
+        <v>0.3084152020172768</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08973813079778015</v>
+        <v>0.2219671022694364</v>
       </c>
       <c r="F7" t="n">
-        <v>1.650660742039468</v>
+        <v>3.567634255893305</v>
       </c>
       <c r="G7" t="n">
-        <v>0.029</v>
+        <v>0.001</v>
       </c>
       <c r="H7" t="n">
-        <v>210.6635293122477</v>
+        <v>380.8718133235855</v>
       </c>
       <c r="I7" t="n">
-        <v>925.3565816780495</v>
+        <v>1234.932035880156</v>
       </c>
       <c r="J7" t="n">
-        <v>3.944363245906707</v>
+        <v>7.408272134187716</v>
       </c>
       <c r="K7" t="n">
-        <v>2.07152114076263</v>
+        <v>1.880831232893278</v>
       </c>
     </row>
     <row r="8">
@@ -698,31 +698,31 @@
         <v>0.17</v>
       </c>
       <c r="C8" t="n">
-        <v>39</v>
+        <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2549791396600926</v>
+        <v>0.2954960837861298</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1420971911237429</v>
+        <v>0.2189195711541874</v>
       </c>
       <c r="F8" t="n">
-        <v>2.258812351896863</v>
+        <v>3.858834434082982</v>
       </c>
       <c r="G8" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H8" t="n">
-        <v>274.3051486143099</v>
+        <v>403.8293337976489</v>
       </c>
       <c r="I8" t="n">
-        <v>1075.794470794671</v>
+        <v>1366.614841805914</v>
       </c>
       <c r="J8" t="n">
-        <v>4.15741950280689</v>
+        <v>6.955016215347848</v>
       </c>
       <c r="K8" t="n">
-        <v>1.747340313866239</v>
+        <v>1.926392208360918</v>
       </c>
     </row>
     <row r="9">
@@ -733,31 +733,31 @@
         <v>0.19</v>
       </c>
       <c r="C9" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2414387621300756</v>
+        <v>0.2843594546144295</v>
       </c>
       <c r="E9" t="n">
-        <v>0.1416280729366645</v>
+        <v>0.2155478637119707</v>
       </c>
       <c r="F9" t="n">
-        <v>2.418966987215371</v>
+        <v>4.132435406376704</v>
       </c>
       <c r="G9" t="n">
         <v>0.001</v>
       </c>
       <c r="H9" t="n">
-        <v>290.2831459440172</v>
+        <v>443.4249848851749</v>
       </c>
       <c r="I9" t="n">
-        <v>1202.305476481969</v>
+        <v>1559.381893900544</v>
       </c>
       <c r="J9" t="n">
-        <v>4.054506171080378</v>
+        <v>6.703915094127846</v>
       </c>
       <c r="K9" t="n">
-        <v>1.638443591008128</v>
+        <v>1.739809103934958</v>
       </c>
     </row>
     <row r="10">
@@ -768,31 +768,31 @@
         <v>0.21</v>
       </c>
       <c r="C10" t="n">
-        <v>48</v>
+        <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2496937919764782</v>
+        <v>0.2890004802438443</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1603716243546304</v>
+        <v>0.2287462836543396</v>
       </c>
       <c r="F10" t="n">
-        <v>2.795429159686045</v>
+        <v>4.796354388603421</v>
       </c>
       <c r="G10" t="n">
         <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>328.2714833978465</v>
+        <v>509.0764720243967</v>
       </c>
       <c r="I10" t="n">
-        <v>1314.696215710363</v>
+        <v>1761.507356648207</v>
       </c>
       <c r="J10" t="n">
-        <v>4.818207844548787</v>
+        <v>6.949935496832635</v>
       </c>
       <c r="K10" t="n">
-        <v>1.508631271790515</v>
+        <v>1.635930364890907</v>
       </c>
     </row>
     <row r="11">
@@ -803,31 +803,31 @@
         <v>0.23</v>
       </c>
       <c r="C11" t="n">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>0.214687990234689</v>
+        <v>0.2727929999649834</v>
       </c>
       <c r="E11" t="n">
-        <v>0.131144159408592</v>
+        <v>0.2168539999622898</v>
       </c>
       <c r="F11" t="n">
-        <v>2.569764734413233</v>
+        <v>4.876615598273971</v>
       </c>
       <c r="G11" t="n">
-        <v>0.002</v>
+        <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>304.9405606050854</v>
+        <v>512.9124948803911</v>
       </c>
       <c r="I11" t="n">
-        <v>1420.389469721784</v>
+        <v>1880.226013666884</v>
       </c>
       <c r="J11" t="n">
-        <v>3.904954691843019</v>
+        <v>6.310557541831615</v>
       </c>
       <c r="K11" t="n">
-        <v>1.198096996920468</v>
+        <v>1.578712521762822</v>
       </c>
     </row>
     <row r="12">
@@ -838,31 +838,31 @@
         <v>0.25</v>
       </c>
       <c r="C12" t="n">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2110129821777128</v>
+        <v>0.2498150152516085</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1351488458486466</v>
+        <v>0.1969850867482006</v>
       </c>
       <c r="F12" t="n">
-        <v>2.781458965833725</v>
+        <v>4.728664647643687</v>
       </c>
       <c r="G12" t="n">
         <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>334.6043940039855</v>
+        <v>505.0133617835027</v>
       </c>
       <c r="I12" t="n">
-        <v>1585.705251642694</v>
+        <v>2021.549270266496</v>
       </c>
       <c r="J12" t="n">
-        <v>3.910343769355727</v>
+        <v>5.588149182702513</v>
       </c>
       <c r="K12" t="n">
-        <v>1.192142318651783</v>
+        <v>1.459078065311562</v>
       </c>
     </row>
     <row r="13">
@@ -873,31 +873,31 @@
         <v>0.27</v>
       </c>
       <c r="C13" t="n">
-        <v>62</v>
+        <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2012329385243729</v>
+        <v>0.2647562312550064</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1299144508926207</v>
+        <v>0.2170131293884485</v>
       </c>
       <c r="F13" t="n">
-        <v>2.821609728510003</v>
+        <v>5.545434228278678</v>
       </c>
       <c r="G13" t="n">
         <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>333.3328444039503</v>
+        <v>595.2875011565457</v>
       </c>
       <c r="I13" t="n">
-        <v>1656.452700279869</v>
+        <v>2248.436225031395</v>
       </c>
       <c r="J13" t="n">
-        <v>3.52811701831622</v>
+        <v>6.207102803980451</v>
       </c>
       <c r="K13" t="n">
-        <v>1.202788401670979</v>
+        <v>1.441795737570718</v>
       </c>
     </row>
     <row r="14">
@@ -908,31 +908,31 @@
         <v>0.29</v>
       </c>
       <c r="C14" t="n">
-        <v>67</v>
+        <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>0.1937500757338941</v>
+        <v>0.2471252105039425</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1276640163678198</v>
+        <v>0.2017713075222523</v>
       </c>
       <c r="F14" t="n">
-        <v>2.931784367118083</v>
+        <v>5.448819048797394</v>
       </c>
       <c r="G14" t="n">
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>337.335698279449</v>
+        <v>596.6607875810586</v>
       </c>
       <c r="I14" t="n">
-        <v>1741.086794426664</v>
+        <v>2414.406795503932</v>
       </c>
       <c r="J14" t="n">
-        <v>3.352202975917723</v>
+        <v>5.87449578957326</v>
       </c>
       <c r="K14" t="n">
-        <v>1.192628746553563</v>
+        <v>1.447474541215652</v>
       </c>
     </row>
     <row r="15">
@@ -943,31 +943,31 @@
         <v>0.31</v>
       </c>
       <c r="C15" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1741406219907763</v>
+        <v>0.2240849783884153</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1115755175961382</v>
+        <v>0.1809785882988828</v>
       </c>
       <c r="F15" t="n">
-        <v>2.783350618139465</v>
+        <v>5.19841670626996</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>318.0656916783984</v>
+        <v>578.8073963978381</v>
       </c>
       <c r="I15" t="n">
-        <v>1826.487628459518</v>
+        <v>2582.981690966221</v>
       </c>
       <c r="J15" t="n">
-        <v>2.90930359930131</v>
+        <v>5.199883648293806</v>
       </c>
       <c r="K15" t="n">
-        <v>1.205088974378534</v>
+        <v>1.482250312541395</v>
       </c>
     </row>
     <row r="16">
@@ -978,31 +978,31 @@
         <v>0.33</v>
       </c>
       <c r="C16" t="n">
-        <v>76</v>
+        <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.1719666503070997</v>
+        <v>0.2084736578922624</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1128214110433211</v>
+        <v>0.1672483275741511</v>
       </c>
       <c r="F16" t="n">
-        <v>2.907531568858063</v>
+        <v>5.056931170316776</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>332.5627216759184</v>
+        <v>569.0610095695224</v>
       </c>
       <c r="I16" t="n">
-        <v>1933.879162512177</v>
+        <v>2729.654265785507</v>
       </c>
       <c r="J16" t="n">
-        <v>3.092673042853001</v>
+        <v>4.867520877420338</v>
       </c>
       <c r="K16" t="n">
-        <v>1.235848094617273</v>
+        <v>1.409034476287008</v>
       </c>
     </row>
     <row r="17">
@@ -1013,31 +1013,31 @@
         <v>0.35</v>
       </c>
       <c r="C17" t="n">
-        <v>81</v>
+        <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>0.162957108944356</v>
+        <v>0.2206453982137992</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1071542495406465</v>
+        <v>0.1824417412634952</v>
       </c>
       <c r="F17" t="n">
-        <v>2.920228652898083</v>
+        <v>5.775504646081888</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>330.4203394156357</v>
+        <v>645.8809151076366</v>
       </c>
       <c r="I17" t="n">
-        <v>2027.652193611648</v>
+        <v>2927.234922351728</v>
       </c>
       <c r="J17" t="n">
-        <v>2.871105600591837</v>
+        <v>5.208016014829071</v>
       </c>
       <c r="K17" t="n">
-        <v>1.238102230181861</v>
+        <v>1.358318743468444</v>
       </c>
     </row>
     <row r="18">
@@ -1048,31 +1048,31 @@
         <v>0.37</v>
       </c>
       <c r="C18" t="n">
-        <v>86</v>
+        <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1449075027891034</v>
+        <v>0.1965117682297473</v>
       </c>
       <c r="E18" t="n">
-        <v>0.09146422171342228</v>
+        <v>0.1593132389811245</v>
       </c>
       <c r="F18" t="n">
-        <v>2.711426017873038</v>
+        <v>5.282783276627061</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>318.7916334033819</v>
+        <v>608.4518092938829</v>
       </c>
       <c r="I18" t="n">
-        <v>2199.966373496529</v>
+        <v>3096.261433984581</v>
       </c>
       <c r="J18" t="n">
-        <v>2.70931798289423</v>
+        <v>4.612550604020796</v>
       </c>
       <c r="K18" t="n">
-        <v>1.256619408695372</v>
+        <v>1.33976585056996</v>
       </c>
     </row>
     <row r="19">
@@ -1083,31 +1083,31 @@
         <v>0.39</v>
       </c>
       <c r="C19" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1415973452455589</v>
+        <v>0.2042663891041457</v>
       </c>
       <c r="E19" t="n">
-        <v>0.09050194912922316</v>
+        <v>0.1693657921350294</v>
       </c>
       <c r="F19" t="n">
-        <v>2.771234905844846</v>
+        <v>5.852805018919915</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>318.4578732463511</v>
+        <v>671.2803094108008</v>
       </c>
       <c r="I19" t="n">
-        <v>2249.038445558988</v>
+        <v>3286.298408440298</v>
       </c>
       <c r="J19" t="n">
-        <v>2.630496794718149</v>
+        <v>4.825015768839927</v>
       </c>
       <c r="K19" t="n">
-        <v>1.215104032616906</v>
+        <v>1.343169374358891</v>
       </c>
     </row>
     <row r="20">
@@ -1118,31 +1118,31 @@
         <v>0.41</v>
       </c>
       <c r="C20" t="n">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1752744235758737</v>
+        <v>0.1877793194559572</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1289415260239566</v>
+        <v>0.1542164814169472</v>
       </c>
       <c r="F20" t="n">
-        <v>3.782936808117261</v>
+        <v>5.594858195177108</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>440.1446200890451</v>
+        <v>651.1066990588542</v>
       </c>
       <c r="I20" t="n">
-        <v>2511.174255258714</v>
+        <v>3467.403657363708</v>
       </c>
       <c r="J20" t="n">
-        <v>3.816690313760467</v>
+        <v>4.357482210157828</v>
       </c>
       <c r="K20" t="n">
-        <v>1.247082934141258</v>
+        <v>1.317841005055362</v>
       </c>
     </row>
     <row r="21">
@@ -1153,31 +1153,31 @@
         <v>0.43</v>
       </c>
       <c r="C21" t="n">
-        <v>100</v>
+        <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1737900241634167</v>
+        <v>0.1799718496166522</v>
       </c>
       <c r="E21" t="n">
-        <v>0.129842685023173</v>
+        <v>0.1476872767669141</v>
       </c>
       <c r="F21" t="n">
-        <v>3.954506178606667</v>
+        <v>5.574546408103156</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>460.4858034505552</v>
+        <v>643.2970843108446</v>
       </c>
       <c r="I21" t="n">
-        <v>2649.667641553207</v>
+        <v>3574.431699630222</v>
       </c>
       <c r="J21" t="n">
-        <v>3.74272018832005</v>
+        <v>4.094312316157855</v>
       </c>
       <c r="K21" t="n">
-        <v>1.24199407636883</v>
+        <v>1.294392964793258</v>
       </c>
     </row>
     <row r="22">
@@ -1188,31 +1188,31 @@
         <v>0.45</v>
       </c>
       <c r="C22" t="n">
-        <v>104</v>
+        <v>139</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1648354030519697</v>
+        <v>0.1745124507798725</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1222249644321723</v>
+        <v>0.1434790842678376</v>
       </c>
       <c r="F22" t="n">
-        <v>3.868427746608191</v>
+        <v>5.623381231043557</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>453.9206353469609</v>
+        <v>649.0349607244868</v>
       </c>
       <c r="I22" t="n">
-        <v>2753.781208056667</v>
+        <v>3719.132691243733</v>
       </c>
       <c r="J22" t="n">
-        <v>3.574642843533844</v>
+        <v>3.947444129863433</v>
       </c>
       <c r="K22" t="n">
-        <v>1.234102768844652</v>
+        <v>1.257886835169517</v>
       </c>
     </row>
     <row r="23">
@@ -1223,31 +1223,31 @@
         <v>0.47</v>
       </c>
       <c r="C23" t="n">
-        <v>109</v>
+        <v>145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1636721350722362</v>
+        <v>0.1659343033095974</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1230736950271991</v>
+        <v>0.1359319401192952</v>
       </c>
       <c r="F23" t="n">
-        <v>4.031488276167008</v>
+        <v>5.530707773154107</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>473.1488443023533</v>
+        <v>633.5592598810028</v>
       </c>
       <c r="I23" t="n">
-        <v>2890.833214178641</v>
+        <v>3818.133124040776</v>
       </c>
       <c r="J23" t="n">
-        <v>3.51431928430009</v>
+        <v>3.638905210546602</v>
       </c>
       <c r="K23" t="n">
-        <v>1.206044823933059</v>
+        <v>1.250459076874172</v>
       </c>
     </row>
     <row r="24">
@@ -1258,31 +1258,31 @@
         <v>0.49</v>
       </c>
       <c r="C24" t="n">
-        <v>114</v>
+        <v>151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1620526385650938</v>
+        <v>0.1559061225631416</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1232587792394036</v>
+        <v>0.1267994371342843</v>
       </c>
       <c r="F24" t="n">
-        <v>4.177275511688499</v>
+        <v>5.356368142439603</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>494.1833339814851</v>
+        <v>613.5640707874595</v>
       </c>
       <c r="I24" t="n">
-        <v>3049.523527399895</v>
+        <v>3935.471299653211</v>
       </c>
       <c r="J24" t="n">
-        <v>3.524583968488105</v>
+        <v>3.32633592070042</v>
       </c>
       <c r="K24" t="n">
-        <v>1.216477571429641</v>
+        <v>1.220861316772881</v>
       </c>
     </row>
     <row r="25">
@@ -1293,31 +1293,31 @@
         <v>0.51</v>
       </c>
       <c r="C25" t="n">
-        <v>118</v>
+        <v>158</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1695281575767169</v>
+        <v>0.1550096860606429</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1324535217542488</v>
+        <v>0.1272139520494798</v>
       </c>
       <c r="F25" t="n">
-        <v>4.572618282442556</v>
+        <v>5.576743754936974</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>541.0020996052117</v>
+        <v>637.4662829940389</v>
       </c>
       <c r="I25" t="n">
-        <v>3191.22266966413</v>
+        <v>4112.42870813021</v>
       </c>
       <c r="J25" t="n">
-        <v>3.806263917930259</v>
+        <v>3.283918311445133</v>
       </c>
       <c r="K25" t="n">
-        <v>1.225943713504539</v>
+        <v>1.216414349107273</v>
       </c>
     </row>
     <row r="26">
@@ -1328,31 +1328,31 @@
         <v>0.53</v>
       </c>
       <c r="C26" t="n">
-        <v>123</v>
+        <v>164</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1670347805709292</v>
+        <v>0.1625211558874616</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1314379763218236</v>
+        <v>0.1360186608206092</v>
       </c>
       <c r="F26" t="n">
-        <v>4.692409447826377</v>
+        <v>6.132296430109785</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>550.4857270068483</v>
+        <v>692.5683544969252</v>
       </c>
       <c r="I26" t="n">
-        <v>3295.635346873709</v>
+        <v>4261.404312042284</v>
       </c>
       <c r="J26" t="n">
-        <v>3.702873691781363</v>
+        <v>3.532923918611982</v>
       </c>
       <c r="K26" t="n">
-        <v>1.227326111231638</v>
+        <v>1.213923259408737</v>
       </c>
     </row>
     <row r="27">
@@ -1363,31 +1363,31 @@
         <v>0.55</v>
       </c>
       <c r="C27" t="n">
-        <v>128</v>
+        <v>170</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1714399604439396</v>
+        <v>0.1616334787205062</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1374825817736093</v>
+        <v>0.1360735238034485</v>
       </c>
       <c r="F27" t="n">
-        <v>5.048680644885354</v>
+        <v>6.323699679635907</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>597.5314478875126</v>
+        <v>720.9853920625444</v>
       </c>
       <c r="I27" t="n">
-        <v>3485.368559000011</v>
+        <v>4460.619159903498</v>
       </c>
       <c r="J27" t="n">
-        <v>3.92203726686862</v>
+        <v>3.513770414967839</v>
       </c>
       <c r="K27" t="n">
-        <v>1.256179197144718</v>
+        <v>1.198533145929196</v>
       </c>
     </row>
     <row r="28">
@@ -1398,31 +1398,31 @@
         <v>0.57</v>
       </c>
       <c r="C28" t="n">
-        <v>132</v>
+        <v>176</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1728618006413</v>
+        <v>0.160047019711321</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1400388562223039</v>
+        <v>0.1353425202910659</v>
       </c>
       <c r="F28" t="n">
-        <v>5.266492805601487</v>
+        <v>6.478456292059015</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>613.248072123656</v>
+        <v>733.1395923602281</v>
       </c>
       <c r="I28" t="n">
-        <v>3547.620526041999</v>
+        <v>4580.776284885542</v>
       </c>
       <c r="J28" t="n">
-        <v>3.901711705248414</v>
+        <v>3.453944288306345</v>
       </c>
       <c r="K28" t="n">
-        <v>1.232262433822034</v>
+        <v>1.200304162233129</v>
       </c>
     </row>
     <row r="29">
@@ -1433,31 +1433,31 @@
         <v>0.59</v>
       </c>
       <c r="C29" t="n">
-        <v>137</v>
+        <v>182</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1851706532066572</v>
+        <v>0.1566359856584542</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1540702964588196</v>
+        <v>0.1326767807055694</v>
       </c>
       <c r="F29" t="n">
-        <v>5.953971998071453</v>
+        <v>6.537611993656506</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>681.036076629953</v>
+        <v>742.2488613926175</v>
       </c>
       <c r="I29" t="n">
-        <v>3677.883427185905</v>
+        <v>4738.686696242945</v>
       </c>
       <c r="J29" t="n">
-        <v>4.214565622679459</v>
+        <v>3.382374361965036</v>
       </c>
       <c r="K29" t="n">
-        <v>1.279991572266424</v>
+        <v>1.196813446469592</v>
       </c>
     </row>
     <row r="30">
@@ -1468,31 +1468,31 @@
         <v>0.61</v>
       </c>
       <c r="C30" t="n">
-        <v>142</v>
+        <v>189</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1952274777393943</v>
+        <v>0.1634790380938957</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1656402526562837</v>
+        <v>0.1406232741073902</v>
       </c>
       <c r="F30" t="n">
-        <v>6.598370654598407</v>
+        <v>7.152639403802755</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>743.0337669506551</v>
+        <v>805.5253846832843</v>
       </c>
       <c r="I30" t="n">
-        <v>3805.989687284276</v>
+        <v>4927.392490654511</v>
       </c>
       <c r="J30" t="n">
-        <v>4.490824554866782</v>
+        <v>3.562683880432621</v>
       </c>
       <c r="K30" t="n">
-        <v>1.295766298011334</v>
+        <v>1.204102465907733</v>
       </c>
     </row>
     <row r="31">
@@ -1503,31 +1503,31 @@
         <v>0.63</v>
       </c>
       <c r="C31" t="n">
-        <v>146</v>
+        <v>195</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1944590370301058</v>
+        <v>0.1619691524977801</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1656897169240381</v>
+        <v>0.1397990242569805</v>
       </c>
       <c r="F31" t="n">
-        <v>6.759250351178545</v>
+        <v>7.305738186922611</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>754.709106785005</v>
+        <v>813.4432202118976</v>
       </c>
       <c r="I31" t="n">
-        <v>3881.069855694917</v>
+        <v>5022.210758453196</v>
       </c>
       <c r="J31" t="n">
-        <v>4.432548524502447</v>
+        <v>3.498712695554342</v>
       </c>
       <c r="K31" t="n">
-        <v>1.272049585058742</v>
+        <v>1.210339920862153</v>
       </c>
     </row>
     <row r="32">
@@ -1538,31 +1538,31 @@
         <v>0.65</v>
       </c>
       <c r="C32" t="n">
-        <v>151</v>
+        <v>201</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1996244098306212</v>
+        <v>0.1660594060824039</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1720252515489183</v>
+        <v>0.1446763139306707</v>
       </c>
       <c r="F32" t="n">
-        <v>7.232989056878782</v>
+        <v>7.765921079330132</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>801.1225415244805</v>
+        <v>863.5315667991919</v>
       </c>
       <c r="I32" t="n">
-        <v>4013.149204569837</v>
+        <v>5200.136428108628</v>
       </c>
       <c r="J32" t="n">
-        <v>4.578095034724645</v>
+        <v>3.626346321482523</v>
       </c>
       <c r="K32" t="n">
-        <v>1.27129152495296</v>
+        <v>1.215761718448286</v>
       </c>
     </row>
     <row r="33">
@@ -1573,31 +1573,31 @@
         <v>0.67</v>
       </c>
       <c r="C33" t="n">
-        <v>156</v>
+        <v>207</v>
       </c>
       <c r="D33" t="n">
-        <v>0.2030297983472427</v>
+        <v>0.1625890446696981</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1764641249588174</v>
+        <v>0.1417579263778996</v>
       </c>
       <c r="F33" t="n">
-        <v>7.642561714084145</v>
+        <v>7.805103998363416</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>848.4257865479465</v>
+        <v>868.0525266234511</v>
       </c>
       <c r="I33" t="n">
-        <v>4178.823963056301</v>
+        <v>5338.936140420233</v>
       </c>
       <c r="J33" t="n">
-        <v>4.740429674420225</v>
+        <v>3.588596807991538</v>
       </c>
       <c r="K33" t="n">
-        <v>1.286237448189681</v>
+        <v>1.192296503212444</v>
       </c>
     </row>
     <row r="34">
@@ -1608,31 +1608,31 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="C34" t="n">
-        <v>160</v>
+        <v>213</v>
       </c>
       <c r="D34" t="n">
-        <v>0.2016068103968351</v>
+        <v>0.1564902148453262</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1756849535915376</v>
+        <v>0.1361155823536674</v>
       </c>
       <c r="F34" t="n">
-        <v>7.7774833767168</v>
+        <v>7.680639879487009</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>860.9921103988788</v>
+        <v>866.6067936029067</v>
       </c>
       <c r="I34" t="n">
-        <v>4270.649928462908</v>
+        <v>5537.769850079472</v>
       </c>
       <c r="J34" t="n">
-        <v>4.689116319364187</v>
+        <v>3.459446255020057</v>
       </c>
       <c r="K34" t="n">
-        <v>1.289054894447494</v>
+        <v>1.188903771530113</v>
       </c>
     </row>
     <row r="35">
@@ -1643,31 +1643,31 @@
         <v>0.71</v>
       </c>
       <c r="C35" t="n">
-        <v>165</v>
+        <v>220</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1984574683180557</v>
+        <v>0.1618093983026529</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1732517283280575</v>
+        <v>0.1422255057396308</v>
       </c>
       <c r="F35" t="n">
-        <v>7.873502955945929</v>
+        <v>8.262371629232579</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>882.6317293133003</v>
+        <v>939.5940910982933</v>
       </c>
       <c r="I35" t="n">
-        <v>4447.460389340251</v>
+        <v>5806.795531992831</v>
       </c>
       <c r="J35" t="n">
-        <v>4.642283505336225</v>
+        <v>3.724392637801692</v>
       </c>
       <c r="K35" t="n">
-        <v>1.29801977536493</v>
+        <v>1.193590081562478</v>
       </c>
     </row>
     <row r="36">
@@ -1678,31 +1678,31 @@
         <v>0.73</v>
       </c>
       <c r="C36" t="n">
-        <v>170</v>
+        <v>226</v>
       </c>
       <c r="D36" t="n">
-        <v>0.1886433320083733</v>
+        <v>0.158626531725474</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1639068482281408</v>
+        <v>0.1395044074465075</v>
       </c>
       <c r="F36" t="n">
-        <v>7.626117506608693</v>
+        <v>8.295445077718496</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>862.9878275018511</v>
+        <v>954.9277224179671</v>
       </c>
       <c r="I36" t="n">
-        <v>4574.706236971821</v>
+        <v>6019.974792556182</v>
       </c>
       <c r="J36" t="n">
-        <v>4.385826029648479</v>
+        <v>3.692477461404551</v>
       </c>
       <c r="K36" t="n">
-        <v>1.291723506782565</v>
+        <v>1.199071020835532</v>
       </c>
     </row>
     <row r="37">
@@ -1713,31 +1713,31 @@
         <v>0.75</v>
       </c>
       <c r="C37" t="n">
-        <v>174</v>
+        <v>232</v>
       </c>
       <c r="D37" t="n">
-        <v>0.1914581169261083</v>
+        <v>0.158582124714781</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1673943704060521</v>
+        <v>0.1399666849960814</v>
       </c>
       <c r="F37" t="n">
-        <v>7.956288800105778</v>
+        <v>8.518849251542653</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>904.7763053110104</v>
+        <v>986.3355369436119</v>
       </c>
       <c r="I37" t="n">
-        <v>4725.714009086392</v>
+        <v>6219.714477388879</v>
       </c>
       <c r="J37" t="n">
-        <v>4.595013398872279</v>
+        <v>3.721437875443694</v>
       </c>
       <c r="K37" t="n">
-        <v>1.289824679652318</v>
+        <v>1.187715497715155</v>
       </c>
     </row>
     <row r="38">
@@ -1748,31 +1748,31 @@
         <v>0.77</v>
       </c>
       <c r="C38" t="n">
-        <v>179</v>
+        <v>238</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1995589659622045</v>
+        <v>0.1618184772343945</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1764248320304763</v>
+        <v>0.1437542202782391</v>
       </c>
       <c r="F38" t="n">
-        <v>8.626169734779298</v>
+        <v>8.957937081339827</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>973.7267267372756</v>
+        <v>1044.741758162253</v>
       </c>
       <c r="I38" t="n">
-        <v>4879.393526832037</v>
+        <v>6456.257505432719</v>
       </c>
       <c r="J38" t="n">
-        <v>4.842942421052491</v>
+        <v>3.91114715608019</v>
       </c>
       <c r="K38" t="n">
-        <v>1.266444647511108</v>
+        <v>1.192758151834497</v>
       </c>
     </row>
     <row r="39">
@@ -1783,31 +1783,31 @@
         <v>0.79</v>
       </c>
       <c r="C39" t="n">
-        <v>184</v>
+        <v>244</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1966699063350408</v>
+        <v>0.1606951368409801</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1741044542658003</v>
+        <v>0.1430626817325974</v>
       </c>
       <c r="F39" t="n">
-        <v>8.715531411982072</v>
+        <v>9.113599657746066</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>983.1318146203869</v>
+        <v>1061.451452343572</v>
       </c>
       <c r="I39" t="n">
-        <v>4998.892982363828</v>
+        <v>6605.373835263965</v>
       </c>
       <c r="J39" t="n">
-        <v>4.769070289625432</v>
+        <v>3.828813568357636</v>
       </c>
       <c r="K39" t="n">
-        <v>1.249385797859496</v>
+        <v>1.20214041714968</v>
       </c>
     </row>
     <row r="40">
@@ -1818,31 +1818,31 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>188</v>
+        <v>251</v>
       </c>
       <c r="D40" t="n">
-        <v>0.213374764181171</v>
+        <v>0.1628716113025655</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1917641807795548</v>
+        <v>0.1457873584720055</v>
       </c>
       <c r="F40" t="n">
-        <v>9.873623502696063</v>
+        <v>9.533434848916819</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>1103.829986324791</v>
+        <v>1100.946124119751</v>
       </c>
       <c r="I40" t="n">
-        <v>5173.198389044535</v>
+        <v>6759.594967563324</v>
       </c>
       <c r="J40" t="n">
-        <v>5.293940708486262</v>
+        <v>3.851913913457008</v>
       </c>
       <c r="K40" t="n">
-        <v>1.261837441994162</v>
+        <v>1.192362665242763</v>
       </c>
     </row>
     <row r="41">
@@ -1853,31 +1853,31 @@
         <v>0.83</v>
       </c>
       <c r="C41" t="n">
-        <v>193</v>
+        <v>257</v>
       </c>
       <c r="D41" t="n">
-        <v>0.2097908305039086</v>
+        <v>0.1599848294057176</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1886622430842269</v>
+        <v>0.1432514594735605</v>
       </c>
       <c r="F41" t="n">
-        <v>9.929240717175698</v>
+        <v>9.560825467574819</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>1107.674704161637</v>
+        <v>1099.284328393614</v>
       </c>
       <c r="I41" t="n">
-        <v>5279.900468009256</v>
+        <v>6871.17855159789</v>
       </c>
       <c r="J41" t="n">
-        <v>5.116677894729317</v>
+        <v>3.727010657560929</v>
       </c>
       <c r="K41" t="n">
-        <v>1.251870844629331</v>
+        <v>1.189011572988112</v>
       </c>
     </row>
     <row r="42">
@@ -1888,31 +1888,31 @@
         <v>0.85</v>
       </c>
       <c r="C42" t="n">
-        <v>198</v>
+        <v>263</v>
       </c>
       <c r="D42" t="n">
-        <v>0.2085799036064721</v>
+        <v>0.1579321619755287</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1879700052628905</v>
+        <v>0.1415495192124068</v>
       </c>
       <c r="F42" t="n">
-        <v>10.12037517746564</v>
+        <v>9.640212770252207</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>1114.138359256528</v>
+        <v>1105.546256053815</v>
       </c>
       <c r="I42" t="n">
-        <v>5341.542209927255</v>
+        <v>7000.133742391987</v>
       </c>
       <c r="J42" t="n">
-        <v>5.024790342344003</v>
+        <v>3.619437175148753</v>
       </c>
       <c r="K42" t="n">
-        <v>1.248302553022435</v>
+        <v>1.194789233715347</v>
       </c>
     </row>
     <row r="43">
@@ -1923,31 +1923,31 @@
         <v>0.87</v>
       </c>
       <c r="C43" t="n">
-        <v>202</v>
+        <v>269</v>
       </c>
       <c r="D43" t="n">
-        <v>0.2077291735271049</v>
+        <v>0.1636913613821015</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1875181830558575</v>
+        <v>0.1477919576060958</v>
       </c>
       <c r="F43" t="n">
-        <v>10.27803035297185</v>
+        <v>10.29544023714485</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>1126.347440984499</v>
+        <v>1185.545046782352</v>
       </c>
       <c r="I43" t="n">
-        <v>5422.191894666788</v>
+        <v>7242.563301889571</v>
       </c>
       <c r="J43" t="n">
-        <v>4.956904069916598</v>
+        <v>3.789437685955459</v>
       </c>
       <c r="K43" t="n">
-        <v>1.237533252696213</v>
+        <v>1.193206724504269</v>
       </c>
     </row>
     <row r="44">
@@ -1958,31 +1958,31 @@
         <v>0.89</v>
       </c>
       <c r="C44" t="n">
-        <v>207</v>
+        <v>275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2051605000095512</v>
+        <v>0.1629597340437462</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1853883731441172</v>
+        <v>0.1474013647880538</v>
       </c>
       <c r="F44" t="n">
-        <v>10.37624841302309</v>
+        <v>10.47408834213926</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>1134.366338289732</v>
+        <v>1201.637993130906</v>
       </c>
       <c r="I44" t="n">
-        <v>5529.165400927186</v>
+        <v>7373.833788955063</v>
       </c>
       <c r="J44" t="n">
-        <v>4.854284703604523</v>
+        <v>3.687582552808328</v>
       </c>
       <c r="K44" t="n">
-        <v>1.231254171188481</v>
+        <v>1.182964090156611</v>
       </c>
     </row>
     <row r="45">
@@ -1993,31 +1993,31 @@
         <v>0.91</v>
       </c>
       <c r="C45" t="n">
-        <v>212</v>
+        <v>282</v>
       </c>
       <c r="D45" t="n">
-        <v>0.205761826316596</v>
+        <v>0.1655014234455269</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1864842007417561</v>
+        <v>0.1503836956093951</v>
       </c>
       <c r="F45" t="n">
-        <v>10.67360840253818</v>
+        <v>10.94750647977498</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>1165.823274156873</v>
+        <v>1263.398181869818</v>
       </c>
       <c r="I45" t="n">
-        <v>5665.887084240181</v>
+        <v>7633.760215274838</v>
       </c>
       <c r="J45" t="n">
-        <v>4.871063128610766</v>
+        <v>3.743292293909736</v>
       </c>
       <c r="K45" t="n">
-        <v>1.228866584940698</v>
+        <v>1.202390387007601</v>
       </c>
     </row>
     <row r="46">
@@ -2028,31 +2028,31 @@
         <v>0.93</v>
       </c>
       <c r="C46" t="n">
-        <v>216</v>
+        <v>288</v>
       </c>
       <c r="D46" t="n">
-        <v>0.200174201909983</v>
+        <v>0.1686256117073743</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1811307305268874</v>
+        <v>0.1538849310638881</v>
       </c>
       <c r="F46" t="n">
-        <v>10.51143449023018</v>
+        <v>11.43947255799805</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>1153.77457530019</v>
+        <v>1319.791572971549</v>
       </c>
       <c r="I46" t="n">
-        <v>5763.852505923987</v>
+        <v>7826.756324904301</v>
       </c>
       <c r="J46" t="n">
-        <v>4.745498337303298</v>
+        <v>3.781007169063533</v>
       </c>
       <c r="K46" t="n">
-        <v>1.241155180706661</v>
+        <v>1.212392119978318</v>
       </c>
     </row>
     <row r="47">
@@ -2063,31 +2063,31 @@
         <v>0.95</v>
       </c>
       <c r="C47" t="n">
-        <v>221</v>
+        <v>294</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1976571646801889</v>
+        <v>0.1737969971193076</v>
       </c>
       <c r="E47" t="n">
-        <v>0.178998028975077</v>
+        <v>0.1594531949859622</v>
       </c>
       <c r="F47" t="n">
-        <v>10.59305038582459</v>
+        <v>12.11652220963631</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>1163.307928747255</v>
+        <v>1397.136919243051</v>
       </c>
       <c r="I47" t="n">
-        <v>5885.483233706697</v>
+        <v>8038.901375746723</v>
       </c>
       <c r="J47" t="n">
-        <v>4.657210249260886</v>
+        <v>3.92554413400088</v>
       </c>
       <c r="K47" t="n">
-        <v>1.238004811282324</v>
+        <v>1.207498767051585</v>
       </c>
     </row>
     <row r="48">
@@ -2098,31 +2098,31 @@
         <v>0.97</v>
       </c>
       <c r="C48" t="n">
-        <v>226</v>
+        <v>300</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1964605135409024</v>
+        <v>0.1714551994232651</v>
       </c>
       <c r="E48" t="n">
-        <v>0.1781982524850138</v>
+        <v>0.157364301454273</v>
       </c>
       <c r="F48" t="n">
-        <v>10.75773218549816</v>
+        <v>12.1677979501777</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>1177.735270782045</v>
+        <v>1396.072920838145</v>
       </c>
       <c r="I48" t="n">
-        <v>5994.768361108068</v>
+        <v>8142.493931558833</v>
       </c>
       <c r="J48" t="n">
-        <v>4.60820141700981</v>
+        <v>3.815192328813844</v>
       </c>
       <c r="K48" t="n">
-        <v>1.24120911180456</v>
+        <v>1.193368184720264</v>
       </c>
     </row>
     <row r="49">
@@ -2133,31 +2133,31 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>230</v>
+        <v>306</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1878631183541706</v>
+        <v>0.1740259980271074</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1697350629602904</v>
+        <v>0.1602597646608925</v>
       </c>
       <c r="F49" t="n">
-        <v>10.36311475623534</v>
+        <v>12.64151154477756</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>1137.955102989095</v>
+        <v>1444.119427195812</v>
       </c>
       <c r="I49" t="n">
-        <v>6057.363004289939</v>
+        <v>8298.297056574651</v>
       </c>
       <c r="J49" t="n">
-        <v>4.377443629440397</v>
+        <v>3.816968739648515</v>
       </c>
       <c r="K49" t="n">
-        <v>1.215481887117924</v>
+        <v>1.206590156777165</v>
       </c>
     </row>
   </sheetData>

--- a/results/01_pollution_assessment/MaxRel_Focus/tables/env_cutoff_metrics.xlsx
+++ b/results/01_pollution_assessment/MaxRel_Focus/tables/env_cutoff_metrics.xlsx
@@ -491,28 +491,28 @@
         <v>15</v>
       </c>
       <c r="D2" t="n">
-        <v>0.406802307573177</v>
+        <v>0.44232770379696</v>
       </c>
       <c r="E2" t="n">
-        <v>0.07724803400271985</v>
+        <v>0.1325097614619377</v>
       </c>
       <c r="F2" t="n">
-        <v>1.234401554456567</v>
+        <v>1.427702025464517</v>
       </c>
       <c r="G2" t="n">
-        <v>0.245</v>
+        <v>0.119</v>
       </c>
       <c r="H2" t="n">
-        <v>127.237518351049</v>
+        <v>145.1602431011881</v>
       </c>
       <c r="I2" t="n">
-        <v>312.7748195680061</v>
+        <v>328.1735280316524</v>
       </c>
       <c r="J2" t="n">
-        <v>5.337160403342086</v>
+        <v>5.849970416022481</v>
       </c>
       <c r="K2" t="n">
-        <v>2.276437896043347</v>
+        <v>6.932494573126395</v>
       </c>
     </row>
     <row r="3">
@@ -526,28 +526,28 @@
         <v>21</v>
       </c>
       <c r="D3" t="n">
-        <v>0.3362461829828328</v>
+        <v>0.3373763217490147</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1149949106437771</v>
+        <v>0.1165017623320196</v>
       </c>
       <c r="F3" t="n">
-        <v>1.519748019652305</v>
+        <v>1.527456682379037</v>
       </c>
       <c r="G3" t="n">
-        <v>0.078</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>150.9542528172882</v>
+        <v>143.7578850841218</v>
       </c>
       <c r="I3" t="n">
-        <v>448.9396771085287</v>
+        <v>426.1054372128343</v>
       </c>
       <c r="J3" t="n">
-        <v>5.615759696666783</v>
+        <v>4.39110326338066</v>
       </c>
       <c r="K3" t="n">
-        <v>1.969355397075732</v>
+        <v>3.208489202715575</v>
       </c>
     </row>
     <row r="4">
@@ -561,28 +561,28 @@
         <v>27</v>
       </c>
       <c r="D4" t="n">
-        <v>0.2972891958586353</v>
+        <v>0.3235721171202644</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1299770996345009</v>
+        <v>0.1625178592917559</v>
       </c>
       <c r="F4" t="n">
-        <v>1.776854169948246</v>
+        <v>2.00908762974032</v>
       </c>
       <c r="G4" t="n">
-        <v>0.021</v>
+        <v>0.002</v>
       </c>
       <c r="H4" t="n">
-        <v>162.0941288826627</v>
+        <v>217.0840059043384</v>
       </c>
       <c r="I4" t="n">
-        <v>545.2405642071851</v>
+        <v>670.8983698482685</v>
       </c>
       <c r="J4" t="n">
-        <v>4.268304743002249</v>
+        <v>4.762539131206578</v>
       </c>
       <c r="K4" t="n">
-        <v>1.697080486963792</v>
+        <v>1.996698983856514</v>
       </c>
     </row>
     <row r="5">
@@ -596,28 +596,28 @@
         <v>34</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2818430561873084</v>
+        <v>0.2388608392344423</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1536007447921849</v>
+        <v>0.1029431319548784</v>
       </c>
       <c r="F5" t="n">
-        <v>2.197738430641119</v>
+        <v>1.757393087444733</v>
       </c>
       <c r="G5" t="n">
-        <v>0.007</v>
+        <v>0.008999999999999999</v>
       </c>
       <c r="H5" t="n">
-        <v>217.3020114734366</v>
+        <v>180.9805005346306</v>
       </c>
       <c r="I5" t="n">
-        <v>771.0036018379717</v>
+        <v>757.681757774442</v>
       </c>
       <c r="J5" t="n">
-        <v>4.560333544169722</v>
+        <v>3.222546157384307</v>
       </c>
       <c r="K5" t="n">
-        <v>1.83573103428303</v>
+        <v>1.39062975460091</v>
       </c>
     </row>
     <row r="6">
@@ -631,28 +631,28 @@
         <v>40</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2652850961007155</v>
+        <v>0.2378685920214412</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1572387867037619</v>
+        <v>0.1257904437893003</v>
       </c>
       <c r="F6" t="n">
-        <v>2.455290676575347</v>
+        <v>2.122345843266056</v>
       </c>
       <c r="G6" t="n">
         <v>0.001</v>
       </c>
       <c r="H6" t="n">
-        <v>247.5942679300839</v>
+        <v>220.9464431772387</v>
       </c>
       <c r="I6" t="n">
-        <v>933.3139010420878</v>
+        <v>928.8592550180933</v>
       </c>
       <c r="J6" t="n">
-        <v>4.898487553407015</v>
+        <v>3.604613589802263</v>
       </c>
       <c r="K6" t="n">
-        <v>1.696756438349829</v>
+        <v>1.233636319386641</v>
       </c>
     </row>
     <row r="7">
@@ -666,28 +666,28 @@
         <v>46</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3084152020172768</v>
+        <v>0.2270897717725003</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2219671022694364</v>
+        <v>0.1304759932440628</v>
       </c>
       <c r="F7" t="n">
-        <v>3.567634255893305</v>
+        <v>2.350490532834902</v>
       </c>
       <c r="G7" t="n">
-        <v>0.001</v>
+        <v>0.002</v>
       </c>
       <c r="H7" t="n">
-        <v>380.8718133235855</v>
+        <v>228.692584249285</v>
       </c>
       <c r="I7" t="n">
-        <v>1234.932035880156</v>
+        <v>1007.058056663117</v>
       </c>
       <c r="J7" t="n">
-        <v>7.408272134187716</v>
+        <v>3.220839712800764</v>
       </c>
       <c r="K7" t="n">
-        <v>1.880831232893278</v>
+        <v>1.183029187265138</v>
       </c>
     </row>
     <row r="8">
@@ -701,28 +701,28 @@
         <v>52</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2954960837861298</v>
+        <v>0.2091560387579398</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2189195711541874</v>
+        <v>0.1231947386229333</v>
       </c>
       <c r="F8" t="n">
-        <v>3.858834434082982</v>
+        <v>2.43314187232452</v>
       </c>
       <c r="G8" t="n">
         <v>0.001</v>
       </c>
       <c r="H8" t="n">
-        <v>403.8293337976489</v>
+        <v>247.6329198605039</v>
       </c>
       <c r="I8" t="n">
-        <v>1366.614841805914</v>
+        <v>1183.962563696734</v>
       </c>
       <c r="J8" t="n">
-        <v>6.955016215347848</v>
+        <v>2.980328087628894</v>
       </c>
       <c r="K8" t="n">
-        <v>1.926392208360918</v>
+        <v>1.21082466727111</v>
       </c>
     </row>
     <row r="9">
@@ -736,28 +736,28 @@
         <v>58</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2843594546144295</v>
+        <v>0.1622596376440491</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2155478637119707</v>
+        <v>0.08170767972520754</v>
       </c>
       <c r="F9" t="n">
-        <v>4.132435406376704</v>
+        <v>2.014347532154719</v>
       </c>
       <c r="G9" t="n">
-        <v>0.001</v>
+        <v>0.004</v>
       </c>
       <c r="H9" t="n">
-        <v>443.4249848851749</v>
+        <v>213.4609530097029</v>
       </c>
       <c r="I9" t="n">
-        <v>1559.381893900544</v>
+        <v>1315.551766964836</v>
       </c>
       <c r="J9" t="n">
-        <v>6.703915094127846</v>
+        <v>2.002404368770054</v>
       </c>
       <c r="K9" t="n">
-        <v>1.739809103934958</v>
+        <v>1.182988148946573</v>
       </c>
     </row>
     <row r="10">
@@ -771,28 +771,28 @@
         <v>65</v>
       </c>
       <c r="D10" t="n">
-        <v>0.2890004802438443</v>
+        <v>0.1527549100866168</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2287462836543396</v>
+        <v>0.08095447873802497</v>
       </c>
       <c r="F10" t="n">
-        <v>4.796354388603421</v>
+        <v>2.127492930299963</v>
       </c>
       <c r="G10" t="n">
         <v>0.001</v>
       </c>
       <c r="H10" t="n">
-        <v>509.0764720243967</v>
+        <v>221.9496967032791</v>
       </c>
       <c r="I10" t="n">
-        <v>1761.507356648207</v>
+        <v>1452.979132241488</v>
       </c>
       <c r="J10" t="n">
-        <v>6.949935496832635</v>
+        <v>2.01488739286279</v>
       </c>
       <c r="K10" t="n">
-        <v>1.635930364890907</v>
+        <v>1.154767132292528</v>
       </c>
     </row>
     <row r="11">
@@ -806,28 +806,28 @@
         <v>71</v>
       </c>
       <c r="D11" t="n">
-        <v>0.2727929999649834</v>
+        <v>0.1695466965987135</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2168539999622898</v>
+        <v>0.105665673260153</v>
       </c>
       <c r="F11" t="n">
-        <v>4.876615598273971</v>
+        <v>2.654101135796458</v>
       </c>
       <c r="G11" t="n">
         <v>0.001</v>
       </c>
       <c r="H11" t="n">
-        <v>512.9124948803911</v>
+        <v>272.5339919565687</v>
       </c>
       <c r="I11" t="n">
-        <v>1880.226013666884</v>
+        <v>1607.4273189858</v>
       </c>
       <c r="J11" t="n">
-        <v>6.310557541831615</v>
+        <v>2.448934174408819</v>
       </c>
       <c r="K11" t="n">
-        <v>1.578712521762822</v>
+        <v>1.124674665692649</v>
       </c>
     </row>
     <row r="12">
@@ -841,28 +841,28 @@
         <v>77</v>
       </c>
       <c r="D12" t="n">
-        <v>0.2498150152516085</v>
+        <v>0.1563863070677459</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1969850867482006</v>
+        <v>0.09697689207251681</v>
       </c>
       <c r="F12" t="n">
-        <v>4.728664647643687</v>
+        <v>2.632348880733877</v>
       </c>
       <c r="G12" t="n">
         <v>0.001</v>
       </c>
       <c r="H12" t="n">
-        <v>505.0133617835027</v>
+        <v>272.7367197010981</v>
       </c>
       <c r="I12" t="n">
-        <v>2021.549270266496</v>
+        <v>1743.993606696971</v>
       </c>
       <c r="J12" t="n">
-        <v>5.588149182702513</v>
+        <v>2.195012752639099</v>
       </c>
       <c r="K12" t="n">
-        <v>1.459078065311562</v>
+        <v>1.074470408641545</v>
       </c>
     </row>
     <row r="13">
@@ -876,28 +876,28 @@
         <v>83</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2647562312550064</v>
+        <v>0.1696998207151658</v>
       </c>
       <c r="E13" t="n">
-        <v>0.2170131293884485</v>
+        <v>0.1157842246577092</v>
       </c>
       <c r="F13" t="n">
-        <v>5.545434228278678</v>
+        <v>3.147508942205149</v>
       </c>
       <c r="G13" t="n">
         <v>0.001</v>
       </c>
       <c r="H13" t="n">
-        <v>595.2875011565457</v>
+        <v>328.9580216555861</v>
       </c>
       <c r="I13" t="n">
-        <v>2248.436225031395</v>
+        <v>1938.470060069943</v>
       </c>
       <c r="J13" t="n">
-        <v>6.207102803980451</v>
+        <v>2.61601347105731</v>
       </c>
       <c r="K13" t="n">
-        <v>1.441795737570718</v>
+        <v>1.07095562531348</v>
       </c>
     </row>
     <row r="14">
@@ -911,28 +911,28 @@
         <v>89</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2471252105039425</v>
+        <v>0.1741762384254558</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2017713075222523</v>
+        <v>0.1244278190534951</v>
       </c>
       <c r="F14" t="n">
-        <v>5.448819048797394</v>
+        <v>3.501141154318282</v>
       </c>
       <c r="G14" t="n">
         <v>0.001</v>
       </c>
       <c r="H14" t="n">
-        <v>596.6607875810586</v>
+        <v>362.7197436588107</v>
       </c>
       <c r="I14" t="n">
-        <v>2414.406795503932</v>
+        <v>2082.486950790639</v>
       </c>
       <c r="J14" t="n">
-        <v>5.87449578957326</v>
+        <v>2.697871423900954</v>
       </c>
       <c r="K14" t="n">
-        <v>1.447474541215652</v>
+        <v>1.083535648415763</v>
       </c>
     </row>
     <row r="15">
@@ -946,28 +946,28 @@
         <v>96</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2240849783884153</v>
+        <v>0.1795907912086195</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1809785882988828</v>
+        <v>0.1340125018313206</v>
       </c>
       <c r="F15" t="n">
-        <v>5.19841670626996</v>
+        <v>3.940270546837766</v>
       </c>
       <c r="G15" t="n">
         <v>0.001</v>
       </c>
       <c r="H15" t="n">
-        <v>578.8073963978381</v>
+        <v>417.4303776969281</v>
       </c>
       <c r="I15" t="n">
-        <v>2582.981690966221</v>
+        <v>2324.341771021127</v>
       </c>
       <c r="J15" t="n">
-        <v>5.199883648293806</v>
+        <v>2.987487235211569</v>
       </c>
       <c r="K15" t="n">
-        <v>1.482250312541395</v>
+        <v>1.107206434417419</v>
       </c>
     </row>
     <row r="16">
@@ -981,28 +981,28 @@
         <v>102</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2084736578922624</v>
+        <v>0.1837030109123888</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1672483275741511</v>
+        <v>0.1411875427307425</v>
       </c>
       <c r="F16" t="n">
-        <v>5.056931170316776</v>
+        <v>4.320851181210605</v>
       </c>
       <c r="G16" t="n">
         <v>0.001</v>
       </c>
       <c r="H16" t="n">
-        <v>569.0610095695224</v>
+        <v>467.9239056404581</v>
       </c>
       <c r="I16" t="n">
-        <v>2729.654265785507</v>
+        <v>2547.176027853018</v>
       </c>
       <c r="J16" t="n">
-        <v>4.867520877420338</v>
+        <v>3.131438330545199</v>
       </c>
       <c r="K16" t="n">
-        <v>1.409034476287008</v>
+        <v>1.114555619114206</v>
       </c>
     </row>
     <row r="17">
@@ -1016,28 +1016,28 @@
         <v>108</v>
       </c>
       <c r="D17" t="n">
-        <v>0.2206453982137992</v>
+        <v>0.1763604711375764</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1824417412634952</v>
+        <v>0.135985984428634</v>
       </c>
       <c r="F17" t="n">
-        <v>5.775504646081888</v>
+        <v>4.368116736912354</v>
       </c>
       <c r="G17" t="n">
         <v>0.001</v>
       </c>
       <c r="H17" t="n">
-        <v>645.8809151076366</v>
+        <v>477.1788869248429</v>
       </c>
       <c r="I17" t="n">
-        <v>2927.234922351728</v>
+        <v>2705.70204222579</v>
       </c>
       <c r="J17" t="n">
-        <v>5.208016014829071</v>
+        <v>3.013981571897542</v>
       </c>
       <c r="K17" t="n">
-        <v>1.358318743468444</v>
+        <v>1.108952207048674</v>
       </c>
     </row>
     <row r="18">
@@ -1051,28 +1051,28 @@
         <v>114</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1965117682297473</v>
+        <v>0.1642875991910907</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1593132389811245</v>
+        <v>0.1255972102647523</v>
       </c>
       <c r="F18" t="n">
-        <v>5.282783276627061</v>
+        <v>4.246212140794798</v>
       </c>
       <c r="G18" t="n">
         <v>0.001</v>
       </c>
       <c r="H18" t="n">
-        <v>608.4518092938829</v>
+        <v>481.0117912648012</v>
       </c>
       <c r="I18" t="n">
-        <v>3096.261433984581</v>
+        <v>2927.864267499055</v>
       </c>
       <c r="J18" t="n">
-        <v>4.612550604020796</v>
+        <v>3.046286037846191</v>
       </c>
       <c r="K18" t="n">
-        <v>1.33976585056996</v>
+        <v>1.142760778171137</v>
       </c>
     </row>
     <row r="19">
@@ -1086,28 +1086,28 @@
         <v>120</v>
       </c>
       <c r="D19" t="n">
-        <v>0.2042663891041457</v>
+        <v>0.168522399798508</v>
       </c>
       <c r="E19" t="n">
-        <v>0.1693657921350294</v>
+        <v>0.1320540840001969</v>
       </c>
       <c r="F19" t="n">
-        <v>5.852805018919915</v>
+        <v>4.621063411058667</v>
       </c>
       <c r="G19" t="n">
         <v>0.001</v>
       </c>
       <c r="H19" t="n">
-        <v>671.2803094108008</v>
+        <v>524.5988637460047</v>
       </c>
       <c r="I19" t="n">
-        <v>3286.298408440298</v>
+        <v>3112.932550054092</v>
       </c>
       <c r="J19" t="n">
-        <v>4.825015768839927</v>
+        <v>3.177572335070344</v>
       </c>
       <c r="K19" t="n">
-        <v>1.343169374358891</v>
+        <v>1.119501053793527</v>
       </c>
     </row>
     <row r="20">
@@ -1121,28 +1121,28 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>0.1877793194559572</v>
+        <v>0.1662474281203444</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1542164814169472</v>
+        <v>0.1317948425054826</v>
       </c>
       <c r="F20" t="n">
-        <v>5.594858195177108</v>
+        <v>4.825397721343456</v>
       </c>
       <c r="G20" t="n">
         <v>0.001</v>
       </c>
       <c r="H20" t="n">
-        <v>651.1066990588542</v>
+        <v>561.6091108781553</v>
       </c>
       <c r="I20" t="n">
-        <v>3467.403657363708</v>
+        <v>3378.152174911323</v>
       </c>
       <c r="J20" t="n">
-        <v>4.357482210157828</v>
+        <v>3.249849212325458</v>
       </c>
       <c r="K20" t="n">
-        <v>1.317841005055362</v>
+        <v>1.126773986335651</v>
       </c>
     </row>
     <row r="21">
@@ -1156,28 +1156,28 @@
         <v>133</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1799718496166522</v>
+        <v>0.1596021919176539</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1476872767669141</v>
+        <v>0.1265156640403963</v>
       </c>
       <c r="F21" t="n">
-        <v>5.574546408103156</v>
+        <v>4.823781827749829</v>
       </c>
       <c r="G21" t="n">
         <v>0.001</v>
       </c>
       <c r="H21" t="n">
-        <v>643.2970843108446</v>
+        <v>564.907471079796</v>
       </c>
       <c r="I21" t="n">
-        <v>3574.431699630222</v>
+        <v>3539.471885018082</v>
       </c>
       <c r="J21" t="n">
-        <v>4.094312316157855</v>
+        <v>3.144054066048789</v>
       </c>
       <c r="K21" t="n">
-        <v>1.294392964793258</v>
+        <v>1.146103367054953</v>
       </c>
     </row>
     <row r="22">
@@ -1191,28 +1191,28 @@
         <v>139</v>
       </c>
       <c r="D22" t="n">
-        <v>0.1745124507798725</v>
+        <v>0.1707519273539801</v>
       </c>
       <c r="E22" t="n">
-        <v>0.1434790842678376</v>
+        <v>0.1395771877808215</v>
       </c>
       <c r="F22" t="n">
-        <v>5.623381231043557</v>
+        <v>5.477252727429261</v>
       </c>
       <c r="G22" t="n">
         <v>0.001</v>
       </c>
       <c r="H22" t="n">
-        <v>649.0349607244868</v>
+        <v>647.2498074575628</v>
       </c>
       <c r="I22" t="n">
-        <v>3719.132691243733</v>
+        <v>3790.585661242763</v>
       </c>
       <c r="J22" t="n">
-        <v>3.947444129863433</v>
+        <v>3.48882413838915</v>
       </c>
       <c r="K22" t="n">
-        <v>1.257886835169517</v>
+        <v>1.125447291106789</v>
       </c>
     </row>
     <row r="23">
@@ -1226,28 +1226,28 @@
         <v>145</v>
       </c>
       <c r="D23" t="n">
-        <v>0.1659343033095974</v>
+        <v>0.1661495971342864</v>
       </c>
       <c r="E23" t="n">
-        <v>0.1359319401192952</v>
+        <v>0.1361549783261673</v>
       </c>
       <c r="F23" t="n">
-        <v>5.530707773154107</v>
+        <v>5.539313508105383</v>
       </c>
       <c r="G23" t="n">
         <v>0.001</v>
       </c>
       <c r="H23" t="n">
-        <v>633.5592598810028</v>
+        <v>651.5666797373271</v>
       </c>
       <c r="I23" t="n">
-        <v>3818.133124040776</v>
+        <v>3921.566413493702</v>
       </c>
       <c r="J23" t="n">
-        <v>3.638905210546602</v>
+        <v>3.405973163942059</v>
       </c>
       <c r="K23" t="n">
-        <v>1.250459076874172</v>
+        <v>1.137982900171051</v>
       </c>
     </row>
     <row r="24">
@@ -1261,28 +1261,28 @@
         <v>151</v>
       </c>
       <c r="D24" t="n">
-        <v>0.1559061225631416</v>
+        <v>0.1656621809210232</v>
       </c>
       <c r="E24" t="n">
-        <v>0.1267994371342843</v>
+        <v>0.1368919112976102</v>
       </c>
       <c r="F24" t="n">
-        <v>5.356368142439603</v>
+        <v>5.758103176975746</v>
       </c>
       <c r="G24" t="n">
         <v>0.001</v>
       </c>
       <c r="H24" t="n">
-        <v>613.5640707874595</v>
+        <v>678.3054777050038</v>
       </c>
       <c r="I24" t="n">
-        <v>3935.471299653211</v>
+        <v>4094.510128587376</v>
       </c>
       <c r="J24" t="n">
-        <v>3.32633592070042</v>
+        <v>3.490429405932755</v>
       </c>
       <c r="K24" t="n">
-        <v>1.220861316772881</v>
+        <v>1.159292487111577</v>
       </c>
     </row>
     <row r="25">
@@ -1296,28 +1296,28 @@
         <v>158</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1550096860606429</v>
+        <v>0.1581944140475021</v>
       </c>
       <c r="E25" t="n">
-        <v>0.1272139520494798</v>
+        <v>0.1305034408253805</v>
       </c>
       <c r="F25" t="n">
-        <v>5.576743754936974</v>
+        <v>5.712851360569895</v>
       </c>
       <c r="G25" t="n">
         <v>0.001</v>
       </c>
       <c r="H25" t="n">
-        <v>637.4662829940389</v>
+        <v>682.3277745604605</v>
       </c>
       <c r="I25" t="n">
-        <v>4112.42870813021</v>
+        <v>4313.222933115535</v>
       </c>
       <c r="J25" t="n">
-        <v>3.283918311445133</v>
+        <v>3.431119657085877</v>
       </c>
       <c r="K25" t="n">
-        <v>1.216414349107273</v>
+        <v>1.147733515030376</v>
       </c>
     </row>
     <row r="26">
@@ -1331,28 +1331,28 @@
         <v>164</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1625211558874616</v>
+        <v>0.1671719930257494</v>
       </c>
       <c r="E26" t="n">
-        <v>0.1360186608206092</v>
+        <v>0.140816676349349</v>
       </c>
       <c r="F26" t="n">
-        <v>6.132296430109785</v>
+        <v>6.343008322698024</v>
       </c>
       <c r="G26" t="n">
         <v>0.001</v>
       </c>
       <c r="H26" t="n">
-        <v>692.5683544969252</v>
+        <v>757.8588050419746</v>
       </c>
       <c r="I26" t="n">
-        <v>4261.404312042284</v>
+        <v>4533.407727724118</v>
       </c>
       <c r="J26" t="n">
-        <v>3.532923918611982</v>
+        <v>3.677387694713539</v>
       </c>
       <c r="K26" t="n">
-        <v>1.213923259408737</v>
+        <v>1.154331706063472</v>
       </c>
     </row>
     <row r="27">
@@ -1366,28 +1366,28 @@
         <v>170</v>
       </c>
       <c r="D27" t="n">
-        <v>0.1616334787205062</v>
+        <v>0.1600483013065211</v>
       </c>
       <c r="E27" t="n">
-        <v>0.1360735238034485</v>
+        <v>0.1344400178097686</v>
       </c>
       <c r="F27" t="n">
-        <v>6.323699679635907</v>
+        <v>6.249864475563857</v>
       </c>
       <c r="G27" t="n">
         <v>0.001</v>
       </c>
       <c r="H27" t="n">
-        <v>720.9853920625444</v>
+        <v>744.046207177269</v>
       </c>
       <c r="I27" t="n">
-        <v>4460.619159903498</v>
+        <v>4648.8853746238</v>
       </c>
       <c r="J27" t="n">
-        <v>3.513770414967839</v>
+        <v>3.484262272776887</v>
       </c>
       <c r="K27" t="n">
-        <v>1.198533145929196</v>
+        <v>1.161354151121751</v>
       </c>
     </row>
     <row r="28">
@@ -1401,28 +1401,28 @@
         <v>176</v>
       </c>
       <c r="D28" t="n">
-        <v>0.160047019711321</v>
+        <v>0.1518922344833368</v>
       </c>
       <c r="E28" t="n">
-        <v>0.1353425202910659</v>
+        <v>0.1269478884387293</v>
       </c>
       <c r="F28" t="n">
-        <v>6.478456292059015</v>
+        <v>6.089245002122299</v>
       </c>
       <c r="G28" t="n">
         <v>0.001</v>
       </c>
       <c r="H28" t="n">
-        <v>733.1395923602281</v>
+        <v>737.9715299419609</v>
       </c>
       <c r="I28" t="n">
-        <v>4580.776284885542</v>
+        <v>4858.520466514825</v>
       </c>
       <c r="J28" t="n">
-        <v>3.453944288306345</v>
+        <v>3.338100827059511</v>
       </c>
       <c r="K28" t="n">
-        <v>1.200304162233129</v>
+        <v>1.15742605091397</v>
       </c>
     </row>
     <row r="29">
@@ -1436,28 +1436,28 @@
         <v>182</v>
       </c>
       <c r="D29" t="n">
-        <v>0.1566359856584542</v>
+        <v>0.1522397121956002</v>
       </c>
       <c r="E29" t="n">
-        <v>0.1326767807055694</v>
+        <v>0.128155613110248</v>
       </c>
       <c r="F29" t="n">
-        <v>6.537611993656506</v>
+        <v>6.321171145164035</v>
       </c>
       <c r="G29" t="n">
         <v>0.001</v>
       </c>
       <c r="H29" t="n">
-        <v>742.2488613926175</v>
+        <v>765.2762627898799</v>
       </c>
       <c r="I29" t="n">
-        <v>4738.686696242945</v>
+        <v>5026.784744618011</v>
       </c>
       <c r="J29" t="n">
-        <v>3.382374361965036</v>
+        <v>3.326221499624795</v>
       </c>
       <c r="K29" t="n">
-        <v>1.196813446469592</v>
+        <v>1.169641128351913</v>
       </c>
     </row>
     <row r="30">
@@ -1471,28 +1471,28 @@
         <v>189</v>
       </c>
       <c r="D30" t="n">
-        <v>0.1634790380938957</v>
+        <v>0.1568379285366996</v>
       </c>
       <c r="E30" t="n">
-        <v>0.1406232741073902</v>
+        <v>0.1338007134693964</v>
       </c>
       <c r="F30" t="n">
-        <v>7.152639403802755</v>
+        <v>6.808024671319738</v>
       </c>
       <c r="G30" t="n">
         <v>0.001</v>
       </c>
       <c r="H30" t="n">
-        <v>805.5253846832843</v>
+        <v>812.4187497630303</v>
       </c>
       <c r="I30" t="n">
-        <v>4927.392490654511</v>
+        <v>5179.989032901098</v>
       </c>
       <c r="J30" t="n">
-        <v>3.562683880432621</v>
+        <v>3.456002137035832</v>
       </c>
       <c r="K30" t="n">
-        <v>1.204102465907733</v>
+        <v>1.171491821904904</v>
       </c>
     </row>
     <row r="31">
@@ -1506,28 +1506,28 @@
         <v>195</v>
       </c>
       <c r="D31" t="n">
-        <v>0.1619691524977801</v>
+        <v>0.1603780646808723</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1397990242569805</v>
+        <v>0.1381658441697843</v>
       </c>
       <c r="F31" t="n">
-        <v>7.305738186922611</v>
+        <v>7.220262584770118</v>
       </c>
       <c r="G31" t="n">
         <v>0.001</v>
       </c>
       <c r="H31" t="n">
-        <v>813.4432202118976</v>
+        <v>868.3894315444788</v>
       </c>
       <c r="I31" t="n">
-        <v>5022.210758453196</v>
+        <v>5414.639672030213</v>
       </c>
       <c r="J31" t="n">
-        <v>3.498712695554342</v>
+        <v>3.622668245972177</v>
       </c>
       <c r="K31" t="n">
-        <v>1.210339920862153</v>
+        <v>1.168533998750039</v>
       </c>
     </row>
     <row r="32">
@@ -1541,28 +1541,28 @@
         <v>201</v>
       </c>
       <c r="D32" t="n">
-        <v>0.1660594060824039</v>
+        <v>0.1590010264945636</v>
       </c>
       <c r="E32" t="n">
-        <v>0.1446763139306707</v>
+        <v>0.1374369502508346</v>
       </c>
       <c r="F32" t="n">
-        <v>7.765921079330132</v>
+        <v>7.373421643359352</v>
       </c>
       <c r="G32" t="n">
         <v>0.001</v>
       </c>
       <c r="H32" t="n">
-        <v>863.5315667991919</v>
+        <v>889.4651594090993</v>
       </c>
       <c r="I32" t="n">
-        <v>5200.136428108628</v>
+        <v>5594.084384351511</v>
       </c>
       <c r="J32" t="n">
-        <v>3.626346321482523</v>
+        <v>3.552985132145266</v>
       </c>
       <c r="K32" t="n">
-        <v>1.215761718448286</v>
+        <v>1.178592319894243</v>
       </c>
     </row>
     <row r="33">
@@ -1576,28 +1576,28 @@
         <v>207</v>
       </c>
       <c r="D33" t="n">
-        <v>0.1625890446696981</v>
+        <v>0.1565756316991339</v>
       </c>
       <c r="E33" t="n">
-        <v>0.1417579263778996</v>
+        <v>0.1355949260200079</v>
       </c>
       <c r="F33" t="n">
-        <v>7.805103998363416</v>
+        <v>7.462839148204296</v>
       </c>
       <c r="G33" t="n">
         <v>0.001</v>
       </c>
       <c r="H33" t="n">
-        <v>868.0525266234511</v>
+        <v>899.6929778660144</v>
       </c>
       <c r="I33" t="n">
-        <v>5338.936140420233</v>
+        <v>5746.060022895575</v>
       </c>
       <c r="J33" t="n">
-        <v>3.588596807991538</v>
+        <v>3.499569609290883</v>
       </c>
       <c r="K33" t="n">
-        <v>1.192296503212444</v>
+        <v>1.172244768018634</v>
       </c>
     </row>
     <row r="34">
@@ -1611,28 +1611,28 @@
         <v>213</v>
       </c>
       <c r="D34" t="n">
-        <v>0.1564902148453262</v>
+        <v>0.1537201713729546</v>
       </c>
       <c r="E34" t="n">
-        <v>0.1361155823536674</v>
+        <v>0.133278629618678</v>
       </c>
       <c r="F34" t="n">
-        <v>7.680639879487009</v>
+        <v>7.519989109470952</v>
       </c>
       <c r="G34" t="n">
         <v>0.001</v>
       </c>
       <c r="H34" t="n">
-        <v>866.6067936029067</v>
+        <v>899.3001266041865</v>
       </c>
       <c r="I34" t="n">
-        <v>5537.769850079472</v>
+        <v>5850.241504235068</v>
       </c>
       <c r="J34" t="n">
-        <v>3.459446255020057</v>
+        <v>3.370680970934915</v>
       </c>
       <c r="K34" t="n">
-        <v>1.188903771530113</v>
+        <v>1.174741521692788</v>
       </c>
     </row>
     <row r="35">
@@ -1646,28 +1646,28 @@
         <v>220</v>
       </c>
       <c r="D35" t="n">
-        <v>0.1618093983026529</v>
+        <v>0.1521421957137687</v>
       </c>
       <c r="E35" t="n">
-        <v>0.1422255057396308</v>
+        <v>0.1323324339313801</v>
       </c>
       <c r="F35" t="n">
-        <v>8.262371629232579</v>
+        <v>7.680162809884326</v>
       </c>
       <c r="G35" t="n">
         <v>0.001</v>
       </c>
       <c r="H35" t="n">
-        <v>939.5940910982933</v>
+        <v>925.051208020794</v>
       </c>
       <c r="I35" t="n">
-        <v>5806.795531992831</v>
+        <v>6080.175218196079</v>
       </c>
       <c r="J35" t="n">
-        <v>3.724392637801692</v>
+        <v>3.383156072027449</v>
       </c>
       <c r="K35" t="n">
-        <v>1.193590081562478</v>
+        <v>1.199185114136166</v>
       </c>
     </row>
     <row r="36">
@@ -1681,28 +1681,28 @@
         <v>226</v>
       </c>
       <c r="D36" t="n">
-        <v>0.158626531725474</v>
+        <v>0.1577692079153603</v>
       </c>
       <c r="E36" t="n">
-        <v>0.1395044074465075</v>
+        <v>0.1386275990043457</v>
       </c>
       <c r="F36" t="n">
-        <v>8.295445077718496</v>
+        <v>8.242212483224229</v>
       </c>
       <c r="G36" t="n">
         <v>0.001</v>
       </c>
       <c r="H36" t="n">
-        <v>954.9277224179671</v>
+        <v>987.5542761148322</v>
       </c>
       <c r="I36" t="n">
-        <v>6019.974792556182</v>
+        <v>6259.486810915813</v>
       </c>
       <c r="J36" t="n">
-        <v>3.692477461404551</v>
+        <v>3.531811151442142</v>
       </c>
       <c r="K36" t="n">
-        <v>1.199071020835532</v>
+        <v>1.201917271774562</v>
       </c>
     </row>
     <row r="37">
@@ -1716,28 +1716,28 @@
         <v>232</v>
       </c>
       <c r="D37" t="n">
-        <v>0.158582124714781</v>
+        <v>0.1585393302799339</v>
       </c>
       <c r="E37" t="n">
-        <v>0.1399666849960814</v>
+        <v>0.1399229437817024</v>
       </c>
       <c r="F37" t="n">
-        <v>8.518849251542653</v>
+        <v>8.516117254817107</v>
       </c>
       <c r="G37" t="n">
         <v>0.001</v>
       </c>
       <c r="H37" t="n">
-        <v>986.3355369436119</v>
+        <v>1007.662292279659</v>
       </c>
       <c r="I37" t="n">
-        <v>6219.714477388879</v>
+        <v>6355.913643008478</v>
       </c>
       <c r="J37" t="n">
-        <v>3.721437875443694</v>
+        <v>3.493007831398028</v>
       </c>
       <c r="K37" t="n">
-        <v>1.187715497715155</v>
+        <v>1.191808315328904</v>
       </c>
     </row>
     <row r="38">
@@ -1751,28 +1751,28 @@
         <v>238</v>
       </c>
       <c r="D38" t="n">
-        <v>0.1618184772343945</v>
+        <v>0.15833690445476</v>
       </c>
       <c r="E38" t="n">
-        <v>0.1437542202782391</v>
+        <v>0.1401976136024919</v>
       </c>
       <c r="F38" t="n">
-        <v>8.957937081339827</v>
+        <v>8.728946778807604</v>
       </c>
       <c r="G38" t="n">
         <v>0.001</v>
       </c>
       <c r="H38" t="n">
-        <v>1044.741758162253</v>
+        <v>1028.283140857209</v>
       </c>
       <c r="I38" t="n">
-        <v>6456.257505432719</v>
+        <v>6494.273362221819</v>
       </c>
       <c r="J38" t="n">
-        <v>3.91114715608019</v>
+        <v>3.533922897091419</v>
       </c>
       <c r="K38" t="n">
-        <v>1.192758151834497</v>
+        <v>1.200788450033399</v>
       </c>
     </row>
     <row r="39">
@@ -1786,28 +1786,28 @@
         <v>244</v>
       </c>
       <c r="D39" t="n">
-        <v>0.1606951368409801</v>
+        <v>0.1578107704529486</v>
       </c>
       <c r="E39" t="n">
-        <v>0.1430626817325974</v>
+        <v>0.1401177194120443</v>
       </c>
       <c r="F39" t="n">
-        <v>9.113599657746066</v>
+        <v>8.919364449246601</v>
       </c>
       <c r="G39" t="n">
         <v>0.001</v>
       </c>
       <c r="H39" t="n">
-        <v>1061.451452343572</v>
+        <v>1050.554483611163</v>
       </c>
       <c r="I39" t="n">
-        <v>6605.373835263965</v>
+        <v>6657.051864051231</v>
       </c>
       <c r="J39" t="n">
-        <v>3.828813568357636</v>
+        <v>3.513363626296417</v>
       </c>
       <c r="K39" t="n">
-        <v>1.20214041714968</v>
+        <v>1.226279287076935</v>
       </c>
     </row>
     <row r="40">
@@ -1821,28 +1821,28 @@
         <v>251</v>
       </c>
       <c r="D40" t="n">
-        <v>0.1628716113025655</v>
+        <v>0.1571214018845243</v>
       </c>
       <c r="E40" t="n">
-        <v>0.1457873584720055</v>
+        <v>0.1399197978413513</v>
       </c>
       <c r="F40" t="n">
-        <v>9.533434848916819</v>
+        <v>9.134113393738016</v>
       </c>
       <c r="G40" t="n">
         <v>0.001</v>
       </c>
       <c r="H40" t="n">
-        <v>1100.946124119751</v>
+        <v>1071.430191261499</v>
       </c>
       <c r="I40" t="n">
-        <v>6759.594967563324</v>
+        <v>6819.12316470383</v>
       </c>
       <c r="J40" t="n">
-        <v>3.851913913457008</v>
+        <v>3.441131956405512</v>
       </c>
       <c r="K40" t="n">
-        <v>1.192362665242763</v>
+        <v>1.21795976808061</v>
       </c>
     </row>
     <row r="41">
@@ -1856,28 +1856,28 @@
         <v>257</v>
       </c>
       <c r="D41" t="n">
-        <v>0.1599848294057176</v>
+        <v>0.1624483667399333</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1432514594735605</v>
+        <v>0.145764071256665</v>
       </c>
       <c r="F41" t="n">
-        <v>9.560825467574819</v>
+        <v>9.736603316744397</v>
       </c>
       <c r="G41" t="n">
         <v>0.001</v>
       </c>
       <c r="H41" t="n">
-        <v>1099.284328393614</v>
+        <v>1138.40060404565</v>
       </c>
       <c r="I41" t="n">
-        <v>6871.17855159789</v>
+        <v>7007.768849213101</v>
       </c>
       <c r="J41" t="n">
-        <v>3.727010657560929</v>
+        <v>3.60053140439609</v>
       </c>
       <c r="K41" t="n">
-        <v>1.189011572988112</v>
+        <v>1.212742567290049</v>
       </c>
     </row>
     <row r="42">
@@ -1891,28 +1891,28 @@
         <v>263</v>
       </c>
       <c r="D42" t="n">
-        <v>0.1579321619755287</v>
+        <v>0.1645603091318159</v>
       </c>
       <c r="E42" t="n">
-        <v>0.1415495192124068</v>
+        <v>0.1483066186479992</v>
       </c>
       <c r="F42" t="n">
-        <v>9.640212770252207</v>
+        <v>10.12448891503517</v>
       </c>
       <c r="G42" t="n">
         <v>0.001</v>
       </c>
       <c r="H42" t="n">
-        <v>1105.546256053815</v>
+        <v>1170.980726499332</v>
       </c>
       <c r="I42" t="n">
-        <v>7000.133742391987</v>
+        <v>7115.815063043876</v>
       </c>
       <c r="J42" t="n">
-        <v>3.619437175148753</v>
+        <v>3.607779212292142</v>
       </c>
       <c r="K42" t="n">
-        <v>1.194789233715347</v>
+        <v>1.231247870576562</v>
       </c>
     </row>
     <row r="43">
@@ -1926,28 +1926,28 @@
         <v>269</v>
       </c>
       <c r="D43" t="n">
-        <v>0.1636913613821015</v>
+        <v>0.1638823489710537</v>
       </c>
       <c r="E43" t="n">
-        <v>0.1477919576060958</v>
+        <v>0.1479865761378037</v>
       </c>
       <c r="F43" t="n">
-        <v>10.29544023714485</v>
+        <v>10.30980693359264</v>
       </c>
       <c r="G43" t="n">
         <v>0.001</v>
       </c>
       <c r="H43" t="n">
-        <v>1185.545046782352</v>
+        <v>1186.394796380652</v>
       </c>
       <c r="I43" t="n">
-        <v>7242.563301889571</v>
+        <v>7239.307978128889</v>
       </c>
       <c r="J43" t="n">
-        <v>3.789437685955459</v>
+        <v>3.586979136238061</v>
       </c>
       <c r="K43" t="n">
-        <v>1.193206724504269</v>
+        <v>1.232452046478739</v>
       </c>
     </row>
     <row r="44">
@@ -1961,28 +1961,28 @@
         <v>275</v>
       </c>
       <c r="D44" t="n">
-        <v>0.1629597340437462</v>
+        <v>0.1688396039431876</v>
       </c>
       <c r="E44" t="n">
-        <v>0.1474013647880538</v>
+        <v>0.1533905259495666</v>
       </c>
       <c r="F44" t="n">
-        <v>10.47408834213926</v>
+        <v>10.9287818996643</v>
       </c>
       <c r="G44" t="n">
         <v>0.001</v>
       </c>
       <c r="H44" t="n">
-        <v>1201.637993130906</v>
+        <v>1256.209843217721</v>
       </c>
       <c r="I44" t="n">
-        <v>7373.833788955063</v>
+        <v>7440.255804203493</v>
       </c>
       <c r="J44" t="n">
-        <v>3.687582552808328</v>
+        <v>3.750848815207922</v>
       </c>
       <c r="K44" t="n">
-        <v>1.182964090156611</v>
+        <v>1.233045161185225</v>
       </c>
     </row>
     <row r="45">
@@ -1996,28 +1996,28 @@
         <v>282</v>
       </c>
       <c r="D45" t="n">
-        <v>0.1655014234455269</v>
+        <v>0.1701538206667479</v>
       </c>
       <c r="E45" t="n">
-        <v>0.1503836956093951</v>
+        <v>0.1551203753889715</v>
       </c>
       <c r="F45" t="n">
-        <v>10.94750647977498</v>
+        <v>11.31835168338182</v>
       </c>
       <c r="G45" t="n">
         <v>0.001</v>
       </c>
       <c r="H45" t="n">
-        <v>1263.398181869818</v>
+        <v>1294.444090901481</v>
       </c>
       <c r="I45" t="n">
-        <v>7633.760215274838</v>
+        <v>7607.493536314381</v>
       </c>
       <c r="J45" t="n">
-        <v>3.743292293909736</v>
+        <v>3.72354784910585</v>
       </c>
       <c r="K45" t="n">
-        <v>1.202390387007601</v>
+        <v>1.233290830810857</v>
       </c>
     </row>
     <row r="46">
@@ -2031,28 +2031,28 @@
         <v>288</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1686256117073743</v>
+        <v>0.1677804730128246</v>
       </c>
       <c r="E46" t="n">
-        <v>0.1538849310638881</v>
+        <v>0.1530248076407115</v>
       </c>
       <c r="F46" t="n">
-        <v>11.43947255799805</v>
+        <v>11.37057996245398</v>
       </c>
       <c r="G46" t="n">
         <v>0.001</v>
       </c>
       <c r="H46" t="n">
-        <v>1319.791572971549</v>
+        <v>1315.121841669554</v>
       </c>
       <c r="I46" t="n">
-        <v>7826.756324904301</v>
+        <v>7838.348635296975</v>
       </c>
       <c r="J46" t="n">
-        <v>3.781007169063533</v>
+        <v>3.694891374260162</v>
       </c>
       <c r="K46" t="n">
-        <v>1.212392119978318</v>
+        <v>1.230505051211993</v>
       </c>
     </row>
     <row r="47">
@@ -2066,28 +2066,28 @@
         <v>294</v>
       </c>
       <c r="D47" t="n">
-        <v>0.1737969971193076</v>
+        <v>0.1707122081671958</v>
       </c>
       <c r="E47" t="n">
-        <v>0.1594531949859622</v>
+        <v>0.1563148506700984</v>
       </c>
       <c r="F47" t="n">
-        <v>12.11652220963631</v>
+        <v>11.85719033521351</v>
       </c>
       <c r="G47" t="n">
         <v>0.001</v>
       </c>
       <c r="H47" t="n">
-        <v>1397.136919243051</v>
+        <v>1367.349724878273</v>
       </c>
       <c r="I47" t="n">
-        <v>8038.901375746723</v>
+        <v>8009.677453993732</v>
       </c>
       <c r="J47" t="n">
-        <v>3.92554413400088</v>
+        <v>3.743287317217725</v>
       </c>
       <c r="K47" t="n">
-        <v>1.207498767051585</v>
+        <v>1.223441692194931</v>
       </c>
     </row>
     <row r="48">
@@ -2101,28 +2101,28 @@
         <v>300</v>
       </c>
       <c r="D48" t="n">
-        <v>0.1714551994232651</v>
+        <v>0.1751239434387609</v>
       </c>
       <c r="E48" t="n">
-        <v>0.157364301454273</v>
+        <v>0.1610954390754746</v>
       </c>
       <c r="F48" t="n">
-        <v>12.1677979501777</v>
+        <v>12.48343650211729</v>
       </c>
       <c r="G48" t="n">
         <v>0.001</v>
       </c>
       <c r="H48" t="n">
-        <v>1396.072920838145</v>
+        <v>1435.188411034148</v>
       </c>
       <c r="I48" t="n">
-        <v>8142.493931558833</v>
+        <v>8195.272347416154</v>
       </c>
       <c r="J48" t="n">
-        <v>3.815192328813844</v>
+        <v>3.862110632880619</v>
       </c>
       <c r="K48" t="n">
-        <v>1.193368184720264</v>
+        <v>1.221347207156406</v>
       </c>
     </row>
     <row r="49">
@@ -2133,31 +2133,31 @@
         <v>0.99</v>
       </c>
       <c r="C49" t="n">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1740259980271074</v>
+        <v>0.1769931352481244</v>
       </c>
       <c r="E49" t="n">
-        <v>0.1602597646608925</v>
+        <v>0.1634568381304948</v>
       </c>
       <c r="F49" t="n">
-        <v>12.64151154477756</v>
+        <v>13.07544697859878</v>
       </c>
       <c r="G49" t="n">
         <v>0.001</v>
       </c>
       <c r="H49" t="n">
-        <v>1444.119427195812</v>
+        <v>1488.341247535601</v>
       </c>
       <c r="I49" t="n">
-        <v>8298.297056574651</v>
+        <v>8409.033748394333</v>
       </c>
       <c r="J49" t="n">
-        <v>3.816968739648515</v>
+        <v>3.860474390864219</v>
       </c>
       <c r="K49" t="n">
-        <v>1.206590156777165</v>
+        <v>1.208415866200727</v>
       </c>
     </row>
   </sheetData>
